--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -32771,208 +32771,208 @@
         <v>2.49</v>
       </c>
       <c r="C151" s="3" t="n">
-        <v>2.1679</v>
+        <v>2.17</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>2.035</v>
+        <v>2.07</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>2.3126</v>
+        <v>2.315</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>2.4675</v>
+        <v>2.465</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>2.12</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>2.1612</v>
+        <v>2.16</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>2.3005</v>
+        <v>2.3</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2.2863</v>
+        <v>2.285</v>
       </c>
       <c r="K151" s="3" t="n">
-        <v>1.409</v>
+        <v>1.415</v>
       </c>
       <c r="L151" s="3" t="n">
-        <v>1.6465</v>
+        <v>1.645</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>2.2633</v>
+        <v>2.335</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>2.32</v>
+        <v>2.305</v>
       </c>
       <c r="O151" s="3" t="n">
-        <v>3.5914</v>
+        <v>3.955</v>
       </c>
       <c r="P151" s="3" t="n">
-        <v>2.052</v>
+        <v>2.05</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>2.7655</v>
+        <v>2.765</v>
       </c>
       <c r="R151" s="3" t="n">
-        <v>2.3275</v>
+        <v>2.33</v>
       </c>
       <c r="S151" s="3" t="n">
-        <v>2.35</v>
+        <v>2.355</v>
       </c>
       <c r="T151" s="3" t="n">
-        <v>2.116</v>
+        <v>2.12</v>
       </c>
       <c r="U151" s="3" t="n">
-        <v>2.6411</v>
+        <v>2.785</v>
       </c>
       <c r="V151" s="3" t="n">
-        <v>2.0811</v>
+        <v>2.08</v>
       </c>
       <c r="W151" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="X151" s="3" t="n">
-        <v>2.1721</v>
+        <v>2.17</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>2.0622</v>
+        <v>2.065</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>2.2399</v>
+        <v>2.24</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>2.26</v>
       </c>
       <c r="AB151" s="3" t="n">
-        <v>2.2617</v>
+        <v>2.26</v>
       </c>
       <c r="AC151" s="3" t="n">
-        <v>2.1892</v>
+        <v>2.635</v>
       </c>
       <c r="AD151" s="3" t="n">
-        <v>2.5265</v>
+        <v>2.73</v>
       </c>
       <c r="AE151" s="3" t="n">
-        <v>1.9392</v>
+        <v>1.94</v>
       </c>
       <c r="AF151" s="3" t="n">
-        <v>3.6929</v>
+        <v>3.695</v>
       </c>
       <c r="AG151" s="3" t="n">
-        <v>2.837</v>
+        <v>2.835</v>
       </c>
       <c r="AH151" s="3" t="n">
-        <v>2.1088</v>
+        <v>2.11</v>
       </c>
       <c r="AI151" s="3" t="n">
-        <v>1.4172</v>
+        <v>1.415</v>
       </c>
       <c r="AJ151" s="3" t="n">
-        <v>2.4707</v>
+        <v>2.47</v>
       </c>
       <c r="AK151" s="3" t="n">
-        <v>2.22</v>
+        <v>2.245</v>
       </c>
       <c r="AL151" s="3" t="n">
-        <v>1.8946</v>
+        <v>1.895</v>
       </c>
       <c r="AM151" s="3" t="n">
-        <v>2.8018</v>
+        <v>2.8</v>
       </c>
       <c r="AN151" s="3" t="n">
-        <v>3.6524</v>
+        <v>3.65</v>
       </c>
       <c r="AO151" s="3" t="n">
-        <v>3.4479</v>
+        <v>3.45</v>
       </c>
       <c r="AP151" s="3" t="n">
-        <v>2.191</v>
+        <v>2.19</v>
       </c>
       <c r="AQ151" s="3" t="n">
-        <v>1.7931</v>
+        <v>1.795</v>
       </c>
       <c r="AR151" s="3" t="n">
-        <v>2.3818</v>
+        <v>2.38</v>
       </c>
       <c r="AS151" s="3" t="n">
-        <v>1.6602</v>
+        <v>1.66</v>
       </c>
       <c r="AT151" s="3" t="n">
-        <v>1.7839</v>
+        <v>1.785</v>
       </c>
       <c r="AU151" s="3" t="n">
-        <v>2.0663</v>
+        <v>2.07</v>
       </c>
       <c r="AV151" s="3" t="n">
-        <v>2.4402</v>
+        <v>2.44</v>
       </c>
       <c r="AW151" s="3" t="n">
-        <v>3.436</v>
+        <v>3.435</v>
       </c>
       <c r="AX151" s="3" t="n">
-        <v>2.3568</v>
+        <v>2.355</v>
       </c>
       <c r="AY151" s="3" t="n">
-        <v>2.0515</v>
+        <v>2.05</v>
       </c>
       <c r="AZ151" s="3" t="n">
-        <v>2.1128</v>
+        <v>2.115</v>
       </c>
       <c r="BA151" s="3" t="n">
-        <v>1.9531</v>
+        <v>1.955</v>
       </c>
       <c r="BB151" s="3" t="n">
-        <v>1.6277</v>
+        <v>1.63</v>
       </c>
       <c r="BC151" s="3" t="n">
-        <v>2.235</v>
+        <v>2.455</v>
       </c>
       <c r="BD151" s="3" t="n">
-        <v>2.035</v>
+        <v>2.075</v>
       </c>
       <c r="BE151" s="3" t="n">
-        <v>2.3334</v>
+        <v>2.335</v>
       </c>
       <c r="BF151" s="3" t="n">
-        <v>1.7839</v>
+        <v>1.785</v>
       </c>
       <c r="BG151" s="3" t="n">
-        <v>2.0453</v>
+        <v>2.045</v>
       </c>
       <c r="BH151" s="3" t="n">
-        <v>2.3536</v>
+        <v>2.355</v>
       </c>
       <c r="BI151" s="3" t="n">
-        <v>3.3519</v>
+        <v>3.35</v>
       </c>
       <c r="BJ151" s="3" t="n">
-        <v>3.4414</v>
+        <v>3.44</v>
       </c>
       <c r="BK151" s="3" t="n">
-        <v>1.6965</v>
+        <v>1.695</v>
       </c>
       <c r="BL151" s="3" t="n">
-        <v>3.4414</v>
+        <v>2.905</v>
       </c>
       <c r="BM151" s="3" t="n">
-        <v>3.4337</v>
+        <v>2.49</v>
       </c>
       <c r="BN151" s="3" t="n">
-        <v>3.4337</v>
+        <v>3.43</v>
       </c>
       <c r="BO151" s="3" t="n">
-        <v>1.7339</v>
+        <v>1.72</v>
       </c>
       <c r="BP151" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="BQ151" s="3" t="n">
-        <v>2.2937</v>
+        <v>2.295</v>
       </c>
       <c r="BR151" s="3" t="n">
-        <v>1.4122</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="152">
@@ -32982,211 +32982,211 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>2.575</v>
+        <v>2.5626</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>2.147</v>
+        <v>2.2769</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>1.419</v>
+        <v>1.75</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>2.312</v>
+        <v>2.4184</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>2.585</v>
+        <v>2.58</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>2.109</v>
+        <v>2.3</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>2.109</v>
+        <v>2.2737</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>2.235</v>
+        <v>2.4471</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>2.185</v>
+        <v>2.4001</v>
       </c>
       <c r="K152" s="3" t="n">
-        <v>1.549</v>
+        <v>1.497</v>
       </c>
       <c r="L152" s="3" t="n">
-        <v>1.5</v>
+        <v>1.5188</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>2.2265</v>
+        <v>2.4436</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>2.31</v>
+        <v>2.385</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>3.6515</v>
+        <v>3.6644</v>
       </c>
       <c r="P152" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.1305</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>2.754</v>
+        <v>2.8491</v>
       </c>
       <c r="R152" s="3" t="n">
-        <v>1.847</v>
+        <v>2.351</v>
       </c>
       <c r="S152" s="3" t="n">
-        <v>2.019</v>
+        <v>2.4129</v>
       </c>
       <c r="T152" s="3" t="n">
-        <v>2.214</v>
+        <v>2.1642</v>
       </c>
       <c r="U152" s="3" t="n">
-        <v>3.055</v>
+        <v>2.666</v>
       </c>
       <c r="V152" s="3" t="n">
-        <v>2.254</v>
+        <v>2.43</v>
       </c>
       <c r="W152" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4417</v>
       </c>
       <c r="X152" s="3" t="n">
-        <v>2.244</v>
+        <v>2.3483</v>
       </c>
       <c r="Y152" s="3" t="n">
-        <v>2.24</v>
+        <v>2.1424</v>
       </c>
       <c r="Z152" s="3" t="n">
-        <v>2.249</v>
+        <v>2.3876</v>
       </c>
       <c r="AA152" s="3" t="n">
-        <v>2.153</v>
+        <v>2.4044</v>
       </c>
       <c r="AB152" s="3" t="n">
-        <v>2.188</v>
+        <v>2.4013</v>
       </c>
       <c r="AC152" s="3" t="n">
-        <v>2.584</v>
+        <v>2.3448</v>
       </c>
       <c r="AD152" s="3" t="n">
-        <v>2.5265</v>
+        <v>2.5775</v>
       </c>
       <c r="AE152" s="3" t="n">
-        <v>2.0065</v>
+        <v>2.1143</v>
       </c>
       <c r="AF152" s="3" t="n">
-        <v>3.581</v>
+        <v>3.6489</v>
       </c>
       <c r="AG152" s="3" t="n">
-        <v>2.5895</v>
+        <v>2.8022</v>
       </c>
       <c r="AH152" s="3" t="n">
-        <v>2.084</v>
+        <v>2.2451</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>1.61</v>
+        <v>1.4992</v>
       </c>
       <c r="AJ152" s="3" t="n">
-        <v>2.605</v>
+        <v>2.5471</v>
       </c>
       <c r="AK152" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.3927</v>
       </c>
       <c r="AL152" s="3" t="n">
-        <v>2.093</v>
+        <v>2.304</v>
       </c>
       <c r="AM152" s="3" t="n">
-        <v>2.98</v>
+        <v>2.7194</v>
       </c>
       <c r="AN152" s="3" t="n">
-        <v>4.0605</v>
+        <v>3.6749</v>
       </c>
       <c r="AO152" s="3" t="n">
-        <v>3.129</v>
+        <v>3.5681</v>
       </c>
       <c r="AP152" s="3" t="n">
-        <v>2.0265</v>
+        <v>2.2911</v>
       </c>
       <c r="AQ152" s="3" t="n">
-        <v>1.6275</v>
+        <v>1.5885</v>
       </c>
       <c r="AR152" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.4352</v>
       </c>
       <c r="AS152" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.476</v>
       </c>
       <c r="AT152" s="3" t="n">
-        <v>1.5395</v>
+        <v>1.5269</v>
       </c>
       <c r="AU152" s="3" t="n">
-        <v>2.205</v>
+        <v>2.1514</v>
       </c>
       <c r="AV152" s="3" t="n">
-        <v>2.5265</v>
+        <v>2.5364</v>
       </c>
       <c r="AW152" s="3" t="n">
-        <v>3.354</v>
+        <v>3.6049</v>
       </c>
       <c r="AX152" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.4512</v>
       </c>
       <c r="AY152" s="3" t="n">
-        <v>2.1645</v>
+        <v>2.1425</v>
       </c>
       <c r="AZ152" s="3" t="n">
-        <v>2.2495</v>
+        <v>2.32</v>
       </c>
       <c r="BA152" s="3" t="n">
-        <v>1.3775</v>
+        <v>1.7248</v>
       </c>
       <c r="BB152" s="3" t="n">
-        <v>1.46</v>
+        <v>1.4214</v>
       </c>
       <c r="BC152" s="3" t="n">
-        <v>1.5095</v>
+        <v>1.95</v>
       </c>
       <c r="BD152" s="3" t="n">
-        <v>1.4095</v>
+        <v>1.75</v>
       </c>
       <c r="BE152" s="3" t="n">
-        <v>2.2475</v>
+        <v>2.4289</v>
       </c>
       <c r="BF152" s="3" t="n">
-        <v>1.5795</v>
+        <v>1.5269</v>
       </c>
       <c r="BG152" s="3" t="n">
-        <v>2.1955</v>
+        <v>2.1473</v>
       </c>
       <c r="BH152" s="3" t="n">
-        <v>2.4385</v>
+        <v>2.4492</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>3.1295</v>
+        <v>3.4973</v>
       </c>
       <c r="BJ152" s="3" t="n">
-        <v>3.1545</v>
+        <v>3.5144</v>
       </c>
       <c r="BK152" s="3" t="n">
-        <v>1.0965</v>
+        <v>1.4694</v>
       </c>
       <c r="BL152" s="3" t="n">
-        <v>2.9735</v>
+        <v>3.5144</v>
       </c>
       <c r="BM152" s="3" t="n">
-        <v>2.22</v>
+        <v>3.514</v>
       </c>
       <c r="BN152" s="3" t="n">
-        <v>3.354</v>
+        <v>3.514</v>
       </c>
       <c r="BO152" s="3" t="n">
-        <v>1.529</v>
+        <v>1.4769</v>
       </c>
       <c r="BP152" s="3" t="n">
-        <v>1.5165</v>
+        <v>1.55</v>
       </c>
       <c r="BQ152" s="3" t="n">
-        <v>2.1765</v>
+        <v>2.4095</v>
       </c>
       <c r="BR152" s="3" t="n">
-        <v>1.5</v>
+        <v>1.4987</v>
       </c>
     </row>
     <row r="153">
@@ -33196,211 +33196,211 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>2.575</v>
+        <v>2.626</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>2.147</v>
+        <v>2.198</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>1.419</v>
+        <v>1.47</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2.312</v>
+        <v>2.363</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2.585</v>
+        <v>2.636</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2.109</v>
+        <v>2.16</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>2.109</v>
+        <v>2.16</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>2.235</v>
+        <v>2.249</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>2.185</v>
+        <v>2.199</v>
       </c>
       <c r="K153" s="3" t="n">
-        <v>1.549</v>
+        <v>1.539</v>
       </c>
       <c r="L153" s="3" t="n">
-        <v>1.5</v>
+        <v>1.4495</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>2.2265</v>
+        <v>2.2775</v>
       </c>
       <c r="N153" s="3" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>3.6515</v>
+        <v>3.7025</v>
       </c>
       <c r="P153" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.2005</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>2.754</v>
+        <v>2.805</v>
       </c>
       <c r="R153" s="3" t="n">
-        <v>1.847</v>
+        <v>1.898</v>
       </c>
       <c r="S153" s="3" t="n">
-        <v>2.019</v>
+        <v>2.07</v>
       </c>
       <c r="T153" s="3" t="n">
-        <v>2.214</v>
+        <v>2.265</v>
       </c>
       <c r="U153" s="3" t="n">
-        <v>3.055</v>
+        <v>3.106</v>
       </c>
       <c r="V153" s="3" t="n">
-        <v>2.254</v>
+        <v>2.305</v>
       </c>
       <c r="W153" s="3" t="n">
+        <v>1.5495</v>
+      </c>
+      <c r="X153" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="Y153" s="3" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="Z153" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA153" s="3" t="n">
+        <v>2.204</v>
+      </c>
+      <c r="AB153" s="3" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="AC153" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AD153" s="3" t="n">
+        <v>2.5775</v>
+      </c>
+      <c r="AE153" s="3" t="n">
+        <v>2.0575</v>
+      </c>
+      <c r="AF153" s="3" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="AG153" s="3" t="n">
+        <v>2.6405</v>
+      </c>
+      <c r="AH153" s="3" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="AI153" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="X153" s="3" t="n">
-        <v>2.244</v>
-      </c>
-      <c r="Y153" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z153" s="3" t="n">
-        <v>2.249</v>
-      </c>
-      <c r="AA153" s="3" t="n">
-        <v>2.153</v>
-      </c>
-      <c r="AB153" s="3" t="n">
-        <v>2.188</v>
-      </c>
-      <c r="AC153" s="3" t="n">
-        <v>2.584</v>
-      </c>
-      <c r="AD153" s="3" t="n">
-        <v>2.5265</v>
-      </c>
-      <c r="AE153" s="3" t="n">
-        <v>2.0065</v>
-      </c>
-      <c r="AF153" s="3" t="n">
-        <v>3.581</v>
-      </c>
-      <c r="AG153" s="3" t="n">
-        <v>2.5895</v>
-      </c>
-      <c r="AH153" s="3" t="n">
-        <v>2.084</v>
-      </c>
-      <c r="AI153" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ153" s="3" t="n">
-        <v>2.605</v>
+        <v>2.656</v>
       </c>
       <c r="AK153" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.155</v>
       </c>
       <c r="AL153" s="3" t="n">
-        <v>2.093</v>
+        <v>2.144</v>
       </c>
       <c r="AM153" s="3" t="n">
-        <v>2.98</v>
+        <v>3.031</v>
       </c>
       <c r="AN153" s="3" t="n">
-        <v>4.0605</v>
+        <v>4.142</v>
       </c>
       <c r="AO153" s="3" t="n">
-        <v>3.129</v>
+        <v>3.18</v>
       </c>
       <c r="AP153" s="3" t="n">
-        <v>2.0265</v>
+        <v>2.0775</v>
       </c>
       <c r="AQ153" s="3" t="n">
-        <v>1.6275</v>
+        <v>1.577</v>
       </c>
       <c r="AR153" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.3775</v>
       </c>
       <c r="AS153" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="AT153" s="3" t="n">
-        <v>1.5395</v>
+        <v>1.5905</v>
       </c>
       <c r="AU153" s="3" t="n">
-        <v>2.205</v>
+        <v>2.256</v>
       </c>
       <c r="AV153" s="3" t="n">
-        <v>2.5265</v>
+        <v>2.5775</v>
       </c>
       <c r="AW153" s="3" t="n">
-        <v>3.354</v>
+        <v>3.405</v>
       </c>
       <c r="AX153" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.3775</v>
       </c>
       <c r="AY153" s="3" t="n">
-        <v>2.1645</v>
+        <v>2.2155</v>
       </c>
       <c r="AZ153" s="3" t="n">
-        <v>2.2495</v>
+        <v>2.3005</v>
       </c>
       <c r="BA153" s="3" t="n">
-        <v>1.3775</v>
+        <v>1.4285</v>
       </c>
       <c r="BB153" s="3" t="n">
-        <v>1.46</v>
+        <v>1.4095</v>
       </c>
       <c r="BC153" s="3" t="n">
-        <v>1.5095</v>
+        <v>1.5605</v>
       </c>
       <c r="BD153" s="3" t="n">
-        <v>1.4095</v>
+        <v>1.4605</v>
       </c>
       <c r="BE153" s="3" t="n">
-        <v>2.2475</v>
+        <v>2.2985</v>
       </c>
       <c r="BF153" s="3" t="n">
-        <v>1.5795</v>
+        <v>1.6305</v>
       </c>
       <c r="BG153" s="3" t="n">
-        <v>2.1955</v>
+        <v>2.2465</v>
       </c>
       <c r="BH153" s="3" t="n">
-        <v>2.4385</v>
+        <v>2.4895</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>3.1295</v>
+        <v>3.1805</v>
       </c>
       <c r="BJ153" s="3" t="n">
-        <v>3.1545</v>
+        <v>3.2055</v>
       </c>
       <c r="BK153" s="3" t="n">
-        <v>1.0965</v>
+        <v>1.1475</v>
       </c>
       <c r="BL153" s="3" t="n">
-        <v>2.9735</v>
+        <v>3.0245</v>
       </c>
       <c r="BM153" s="3" t="n">
-        <v>2.22</v>
+        <v>2.271</v>
       </c>
       <c r="BN153" s="3" t="n">
-        <v>3.354</v>
+        <v>3.405</v>
       </c>
       <c r="BO153" s="3" t="n">
-        <v>1.529</v>
+        <v>1.58</v>
       </c>
       <c r="BP153" s="3" t="n">
-        <v>1.5165</v>
+        <v>1.5675</v>
       </c>
       <c r="BQ153" s="3" t="n">
-        <v>2.1765</v>
+        <v>2.2275</v>
       </c>
       <c r="BR153" s="3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="154">
@@ -33410,211 +33410,211 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>2.575</v>
+        <v>2.626</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2.147</v>
+        <v>2.198</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1.419</v>
+        <v>1.47</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2.312</v>
+        <v>2.363</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2.585</v>
+        <v>2.636</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2.109</v>
+        <v>2.16</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>2.109</v>
+        <v>2.16</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>2.235</v>
+        <v>2.249</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>2.185</v>
+        <v>2.199</v>
       </c>
       <c r="K154" s="3" t="n">
-        <v>1.549</v>
+        <v>1.539</v>
       </c>
       <c r="L154" s="3" t="n">
-        <v>1.5</v>
+        <v>1.4495</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>2.2265</v>
+        <v>2.2775</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>3.6515</v>
+        <v>3.7025</v>
       </c>
       <c r="P154" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.2005</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>2.754</v>
+        <v>2.805</v>
       </c>
       <c r="R154" s="3" t="n">
-        <v>1.847</v>
+        <v>1.898</v>
       </c>
       <c r="S154" s="3" t="n">
-        <v>2.019</v>
+        <v>2.07</v>
       </c>
       <c r="T154" s="3" t="n">
-        <v>2.214</v>
+        <v>2.265</v>
       </c>
       <c r="U154" s="3" t="n">
-        <v>3.055</v>
+        <v>3.106</v>
       </c>
       <c r="V154" s="3" t="n">
-        <v>2.254</v>
+        <v>2.305</v>
       </c>
       <c r="W154" s="3" t="n">
+        <v>1.5495</v>
+      </c>
+      <c r="X154" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="Y154" s="3" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="Z154" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA154" s="3" t="n">
+        <v>2.204</v>
+      </c>
+      <c r="AB154" s="3" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="AC154" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AD154" s="3" t="n">
+        <v>2.5775</v>
+      </c>
+      <c r="AE154" s="3" t="n">
+        <v>2.0575</v>
+      </c>
+      <c r="AF154" s="3" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="AG154" s="3" t="n">
+        <v>2.6405</v>
+      </c>
+      <c r="AH154" s="3" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="AI154" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="X154" s="3" t="n">
-        <v>2.244</v>
-      </c>
-      <c r="Y154" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z154" s="3" t="n">
-        <v>2.249</v>
-      </c>
-      <c r="AA154" s="3" t="n">
-        <v>2.153</v>
-      </c>
-      <c r="AB154" s="3" t="n">
-        <v>2.188</v>
-      </c>
-      <c r="AC154" s="3" t="n">
-        <v>2.584</v>
-      </c>
-      <c r="AD154" s="3" t="n">
-        <v>2.5265</v>
-      </c>
-      <c r="AE154" s="3" t="n">
-        <v>2.0065</v>
-      </c>
-      <c r="AF154" s="3" t="n">
-        <v>3.581</v>
-      </c>
-      <c r="AG154" s="3" t="n">
-        <v>2.5895</v>
-      </c>
-      <c r="AH154" s="3" t="n">
-        <v>2.084</v>
-      </c>
-      <c r="AI154" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ154" s="3" t="n">
-        <v>2.605</v>
+        <v>2.656</v>
       </c>
       <c r="AK154" s="3" t="n">
-        <v>2.1495</v>
+        <v>2.155</v>
       </c>
       <c r="AL154" s="3" t="n">
-        <v>2.093</v>
+        <v>2.144</v>
       </c>
       <c r="AM154" s="3" t="n">
-        <v>2.98</v>
+        <v>3.031</v>
       </c>
       <c r="AN154" s="3" t="n">
-        <v>4.0605</v>
+        <v>4.142</v>
       </c>
       <c r="AO154" s="3" t="n">
-        <v>3.129</v>
+        <v>3.18</v>
       </c>
       <c r="AP154" s="3" t="n">
-        <v>2.0265</v>
+        <v>2.0775</v>
       </c>
       <c r="AQ154" s="3" t="n">
-        <v>1.6275</v>
+        <v>1.577</v>
       </c>
       <c r="AR154" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.3775</v>
       </c>
       <c r="AS154" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="AT154" s="3" t="n">
-        <v>1.5395</v>
+        <v>1.5905</v>
       </c>
       <c r="AU154" s="3" t="n">
-        <v>2.205</v>
+        <v>2.256</v>
       </c>
       <c r="AV154" s="3" t="n">
-        <v>2.5265</v>
+        <v>2.5775</v>
       </c>
       <c r="AW154" s="3" t="n">
-        <v>3.354</v>
+        <v>3.405</v>
       </c>
       <c r="AX154" s="3" t="n">
-        <v>2.3265</v>
+        <v>2.3775</v>
       </c>
       <c r="AY154" s="3" t="n">
-        <v>2.1645</v>
+        <v>2.2155</v>
       </c>
       <c r="AZ154" s="3" t="n">
-        <v>2.2495</v>
+        <v>2.3005</v>
       </c>
       <c r="BA154" s="3" t="n">
-        <v>1.3775</v>
+        <v>1.4285</v>
       </c>
       <c r="BB154" s="3" t="n">
-        <v>1.46</v>
+        <v>1.4095</v>
       </c>
       <c r="BC154" s="3" t="n">
-        <v>1.5095</v>
+        <v>1.5605</v>
       </c>
       <c r="BD154" s="3" t="n">
-        <v>1.4095</v>
+        <v>1.4605</v>
       </c>
       <c r="BE154" s="3" t="n">
-        <v>2.2475</v>
+        <v>2.2985</v>
       </c>
       <c r="BF154" s="3" t="n">
-        <v>1.5795</v>
+        <v>1.6305</v>
       </c>
       <c r="BG154" s="3" t="n">
-        <v>2.1955</v>
+        <v>2.2465</v>
       </c>
       <c r="BH154" s="3" t="n">
-        <v>2.4385</v>
+        <v>2.4895</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>3.1295</v>
+        <v>3.1805</v>
       </c>
       <c r="BJ154" s="3" t="n">
-        <v>3.1545</v>
+        <v>3.2055</v>
       </c>
       <c r="BK154" s="3" t="n">
-        <v>1.0965</v>
+        <v>1.1475</v>
       </c>
       <c r="BL154" s="3" t="n">
-        <v>2.9735</v>
+        <v>3.0245</v>
       </c>
       <c r="BM154" s="3" t="n">
-        <v>2.22</v>
+        <v>2.271</v>
       </c>
       <c r="BN154" s="3" t="n">
-        <v>3.354</v>
+        <v>3.405</v>
       </c>
       <c r="BO154" s="3" t="n">
-        <v>1.529</v>
+        <v>1.58</v>
       </c>
       <c r="BP154" s="3" t="n">
-        <v>1.5165</v>
+        <v>1.5675</v>
       </c>
       <c r="BQ154" s="3" t="n">
-        <v>2.1765</v>
+        <v>2.2275</v>
       </c>
       <c r="BR154" s="3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="155">
@@ -33624,211 +33624,211 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K155" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L155" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P155" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R155" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S155" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T155" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U155" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V155" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W155" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X155" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA155" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB155" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC155" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD155" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE155" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF155" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG155" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH155" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ155" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK155" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL155" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM155" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN155" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO155" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP155" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ155" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR155" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS155" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT155" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU155" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV155" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW155" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX155" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY155" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ155" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA155" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB155" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC155" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD155" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE155" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF155" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG155" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH155" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ155" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK155" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL155" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM155" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN155" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO155" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP155" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ155" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR155" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="156">
@@ -33838,211 +33838,211 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K156" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L156" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P156" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R156" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S156" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T156" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U156" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V156" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W156" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X156" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA156" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB156" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC156" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD156" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE156" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF156" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG156" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH156" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ156" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK156" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL156" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM156" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN156" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO156" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP156" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ156" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR156" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS156" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT156" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU156" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV156" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW156" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX156" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY156" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ156" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA156" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB156" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC156" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD156" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE156" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF156" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG156" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH156" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ156" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK156" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL156" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM156" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN156" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO156" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP156" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ156" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR156" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="157">
@@ -34052,211 +34052,211 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K157" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L157" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P157" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R157" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S157" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T157" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U157" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V157" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W157" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X157" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA157" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB157" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC157" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD157" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE157" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF157" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG157" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH157" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ157" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK157" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL157" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM157" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN157" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO157" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP157" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ157" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR157" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS157" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT157" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU157" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV157" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW157" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX157" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY157" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ157" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA157" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB157" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC157" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD157" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE157" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF157" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG157" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH157" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ157" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK157" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL157" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM157" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN157" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO157" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP157" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ157" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR157" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="158">
@@ -34266,211 +34266,211 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K158" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L158" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O158" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P158" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R158" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S158" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T158" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U158" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V158" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W158" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X158" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA158" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB158" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC158" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD158" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE158" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF158" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG158" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH158" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ158" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK158" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL158" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM158" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN158" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO158" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP158" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ158" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR158" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS158" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT158" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU158" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV158" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW158" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX158" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY158" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ158" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA158" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB158" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC158" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD158" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE158" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF158" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG158" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH158" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ158" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK158" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL158" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM158" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN158" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO158" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP158" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ158" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR158" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="159">
@@ -34480,211 +34480,211 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C159" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K159" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L159" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P159" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R159" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S159" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T159" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U159" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V159" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W159" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X159" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA159" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB159" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC159" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD159" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE159" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF159" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG159" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH159" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ159" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK159" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL159" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM159" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN159" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO159" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP159" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ159" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR159" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS159" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT159" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU159" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV159" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW159" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX159" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY159" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ159" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA159" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB159" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC159" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD159" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE159" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF159" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG159" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH159" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ159" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK159" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL159" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM159" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN159" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO159" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP159" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ159" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR159" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="160">
@@ -34694,211 +34694,211 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K160" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L160" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P160" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R160" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S160" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T160" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U160" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V160" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W160" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X160" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA160" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB160" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC160" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD160" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE160" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF160" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG160" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH160" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ160" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK160" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL160" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM160" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN160" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO160" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP160" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ160" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR160" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS160" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT160" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU160" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV160" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW160" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX160" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY160" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ160" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA160" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB160" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC160" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD160" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE160" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF160" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG160" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH160" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ160" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK160" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL160" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM160" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN160" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO160" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP160" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ160" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR160" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="161">
@@ -34908,211 +34908,211 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C161" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K161" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L161" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M161" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P161" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q161" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R161" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S161" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T161" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U161" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V161" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W161" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X161" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA161" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB161" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC161" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD161" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE161" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF161" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG161" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH161" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ161" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK161" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL161" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM161" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN161" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO161" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP161" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ161" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR161" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS161" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT161" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU161" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV161" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW161" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX161" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY161" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ161" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA161" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB161" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC161" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD161" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE161" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF161" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG161" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH161" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ161" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK161" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL161" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM161" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN161" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO161" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP161" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ161" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR161" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="162">
@@ -35122,211 +35122,211 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K162" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P162" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R162" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S162" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T162" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U162" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V162" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W162" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X162" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA162" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB162" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC162" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD162" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE162" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF162" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG162" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH162" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ162" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK162" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL162" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM162" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN162" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO162" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP162" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ162" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR162" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS162" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT162" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU162" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV162" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW162" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX162" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY162" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ162" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA162" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB162" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC162" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD162" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE162" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF162" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG162" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH162" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ162" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK162" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL162" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM162" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN162" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO162" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP162" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ162" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR162" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="163">
@@ -35336,211 +35336,211 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K163" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L163" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O163" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P163" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R163" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S163" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T163" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U163" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V163" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W163" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X163" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA163" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB163" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC163" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD163" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE163" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF163" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG163" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH163" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ163" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK163" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL163" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM163" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN163" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO163" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP163" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ163" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR163" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS163" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT163" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU163" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV163" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW163" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX163" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY163" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ163" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA163" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB163" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC163" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD163" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE163" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF163" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG163" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH163" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ163" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK163" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL163" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM163" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN163" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO163" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP163" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ163" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR163" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="164">
@@ -35550,211 +35550,211 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K164" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L164" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O164" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P164" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R164" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S164" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T164" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U164" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V164" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W164" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X164" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y164" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA164" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB164" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC164" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD164" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE164" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF164" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG164" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH164" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI164" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ164" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM164" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN164" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO164" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP164" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ164" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR164" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS164" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT164" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU164" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV164" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW164" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX164" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY164" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ164" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA164" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB164" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC164" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD164" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE164" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF164" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG164" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH164" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ164" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK164" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL164" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM164" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN164" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO164" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP164" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ164" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR164" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="165">
@@ -35764,211 +35764,211 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K165" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L165" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N165" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O165" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P165" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R165" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S165" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T165" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U165" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V165" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W165" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X165" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA165" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB165" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC165" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD165" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE165" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF165" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG165" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH165" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI165" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ165" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK165" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL165" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM165" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN165" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO165" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP165" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ165" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR165" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS165" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT165" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU165" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV165" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW165" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX165" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY165" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ165" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA165" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB165" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC165" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD165" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE165" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF165" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG165" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH165" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ165" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK165" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL165" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM165" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN165" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO165" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP165" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ165" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR165" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="166">
@@ -35978,211 +35978,211 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K166" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N166" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P166" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R166" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S166" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T166" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U166" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V166" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W166" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X166" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA166" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB166" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC166" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD166" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE166" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF166" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG166" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH166" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI166" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ166" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK166" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL166" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM166" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN166" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO166" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP166" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ166" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR166" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS166" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT166" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU166" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV166" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW166" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX166" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY166" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ166" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA166" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB166" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC166" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD166" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE166" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF166" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG166" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH166" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI166" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ166" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK166" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL166" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM166" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN166" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO166" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP166" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ166" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR166" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="167">
@@ -36192,211 +36192,211 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C167" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K167" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P167" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R167" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S167" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T167" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U167" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V167" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W167" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X167" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA167" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC167" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD167" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE167" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF167" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG167" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH167" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ167" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM167" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN167" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO167" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP167" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ167" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR167" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS167" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT167" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU167" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV167" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW167" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX167" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY167" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ167" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA167" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB167" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC167" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD167" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE167" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF167" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG167" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH167" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI167" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ167" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK167" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL167" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM167" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN167" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO167" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP167" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ167" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR167" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="168">
@@ -36406,211 +36406,211 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K168" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L168" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N168" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O168" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P168" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R168" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S168" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T168" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U168" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V168" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W168" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X168" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA168" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC168" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD168" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE168" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF168" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG168" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH168" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ168" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM168" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN168" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO168" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP168" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ168" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR168" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS168" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT168" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU168" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV168" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW168" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX168" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY168" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ168" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA168" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB168" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC168" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD168" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE168" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF168" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG168" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH168" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI168" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ168" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK168" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL168" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM168" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN168" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO168" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP168" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ168" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR168" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="169">
@@ -36620,211 +36620,211 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K169" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L169" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O169" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P169" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R169" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S169" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T169" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U169" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V169" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W169" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X169" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA169" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB169" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC169" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD169" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE169" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF169" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG169" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH169" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ169" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK169" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM169" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN169" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO169" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP169" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ169" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR169" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS169" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT169" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU169" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV169" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW169" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX169" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY169" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ169" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA169" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB169" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC169" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD169" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE169" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF169" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG169" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH169" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI169" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ169" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK169" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL169" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM169" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN169" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO169" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP169" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ169" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR169" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="170">
@@ -36834,211 +36834,211 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K170" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L170" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O170" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P170" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R170" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S170" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T170" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U170" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V170" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W170" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X170" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA170" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB170" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC170" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD170" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE170" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF170" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG170" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH170" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI170" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ170" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK170" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL170" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM170" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN170" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO170" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP170" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ170" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR170" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS170" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT170" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU170" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV170" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW170" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX170" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY170" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ170" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA170" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB170" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC170" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD170" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE170" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF170" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG170" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH170" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI170" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ170" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK170" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL170" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM170" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN170" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO170" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP170" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ170" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR170" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="171">
@@ -37048,211 +37048,211 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C171" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K171" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L171" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M171" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N171" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P171" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R171" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S171" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T171" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U171" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V171" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W171" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X171" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA171" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB171" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC171" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD171" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE171" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF171" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG171" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH171" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI171" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ171" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK171" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL171" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM171" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN171" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO171" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP171" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ171" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR171" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS171" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT171" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU171" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV171" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW171" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX171" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY171" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ171" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA171" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB171" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC171" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD171" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE171" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF171" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG171" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH171" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI171" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ171" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK171" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL171" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM171" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN171" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO171" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP171" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ171" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR171" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="172">
@@ -37262,211 +37262,211 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K172" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L172" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O172" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P172" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R172" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S172" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T172" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U172" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V172" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W172" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X172" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA172" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB172" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC172" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD172" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE172" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF172" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG172" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH172" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI172" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ172" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK172" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL172" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM172" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN172" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO172" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP172" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ172" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR172" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS172" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT172" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU172" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV172" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW172" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX172" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY172" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ172" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA172" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB172" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC172" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD172" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE172" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF172" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG172" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH172" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI172" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ172" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK172" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL172" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM172" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN172" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO172" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP172" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ172" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR172" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="173">
@@ -37476,211 +37476,211 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K173" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L173" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P173" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R173" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S173" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T173" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U173" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V173" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W173" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X173" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA173" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB173" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC173" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD173" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE173" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF173" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG173" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH173" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI173" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ173" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK173" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM173" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN173" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO173" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP173" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ173" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR173" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS173" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT173" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU173" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV173" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW173" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX173" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY173" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ173" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA173" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB173" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC173" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD173" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE173" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF173" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG173" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH173" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI173" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ173" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK173" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL173" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM173" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN173" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO173" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP173" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ173" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR173" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="174">
@@ -37690,211 +37690,211 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K174" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L174" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N174" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O174" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P174" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R174" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S174" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T174" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U174" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V174" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W174" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X174" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA174" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB174" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC174" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD174" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE174" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF174" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG174" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH174" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI174" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ174" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK174" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM174" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN174" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO174" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP174" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ174" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR174" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS174" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT174" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU174" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV174" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW174" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX174" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY174" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ174" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA174" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB174" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC174" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD174" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE174" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF174" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG174" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH174" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI174" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ174" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK174" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL174" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM174" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN174" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO174" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP174" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ174" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR174" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="175">
@@ -37904,211 +37904,211 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C175" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L175" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P175" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R175" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S175" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T175" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U175" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V175" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W175" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X175" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA175" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB175" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC175" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD175" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE175" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF175" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG175" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH175" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ175" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK175" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM175" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN175" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO175" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP175" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ175" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR175" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS175" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT175" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU175" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV175" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW175" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX175" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY175" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ175" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA175" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB175" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC175" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD175" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE175" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF175" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG175" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH175" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI175" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ175" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK175" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL175" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM175" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN175" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO175" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP175" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ175" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR175" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="176">
@@ -38118,211 +38118,211 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P176" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R176" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S176" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T176" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U176" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V176" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W176" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X176" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA176" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB176" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC176" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD176" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE176" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF176" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG176" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH176" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ176" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK176" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL176" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM176" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN176" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO176" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP176" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ176" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR176" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS176" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT176" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU176" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV176" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW176" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX176" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY176" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ176" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA176" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB176" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC176" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD176" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE176" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF176" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG176" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH176" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI176" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ176" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK176" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL176" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM176" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN176" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO176" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP176" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ176" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR176" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="177">
@@ -38332,211 +38332,211 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K177" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L177" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O177" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P177" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R177" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S177" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T177" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U177" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V177" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W177" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X177" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA177" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB177" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC177" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD177" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE177" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF177" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG177" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH177" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ177" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL177" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM177" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN177" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO177" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP177" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ177" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR177" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS177" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT177" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU177" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV177" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW177" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX177" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY177" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ177" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA177" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB177" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC177" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD177" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE177" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF177" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG177" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH177" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI177" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ177" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK177" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL177" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM177" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN177" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO177" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP177" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ177" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR177" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="178">
@@ -38546,211 +38546,211 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L178" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P178" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R178" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S178" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T178" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U178" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V178" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W178" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X178" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA178" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB178" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC178" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD178" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE178" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF178" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG178" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH178" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ178" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK178" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL178" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM178" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN178" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO178" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP178" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ178" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR178" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS178" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT178" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU178" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV178" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW178" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX178" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY178" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ178" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA178" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB178" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC178" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD178" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE178" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF178" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG178" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH178" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI178" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ178" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK178" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL178" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM178" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN178" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO178" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP178" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ178" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR178" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="179">
@@ -38760,211 +38760,211 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C179" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K179" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L179" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M179" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N179" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O179" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P179" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q179" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R179" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S179" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T179" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U179" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V179" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W179" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X179" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y179" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z179" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA179" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB179" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC179" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD179" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE179" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF179" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG179" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH179" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ179" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK179" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM179" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN179" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO179" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP179" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ179" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR179" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS179" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT179" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU179" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV179" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW179" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX179" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY179" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ179" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA179" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB179" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC179" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD179" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE179" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF179" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG179" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH179" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI179" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ179" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK179" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL179" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM179" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN179" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO179" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP179" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ179" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR179" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="180">
@@ -38974,211 +38974,211 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K180" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L180" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P180" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R180" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S180" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T180" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U180" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V180" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W180" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X180" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA180" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB180" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC180" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD180" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE180" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF180" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG180" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH180" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ180" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK180" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL180" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM180" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN180" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO180" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP180" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ180" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR180" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS180" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT180" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU180" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV180" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW180" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX180" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY180" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ180" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA180" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB180" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC180" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD180" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE180" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF180" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG180" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH180" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI180" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ180" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK180" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL180" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM180" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN180" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO180" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP180" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ180" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR180" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="181">
@@ -39188,211 +39188,211 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C181" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K181" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L181" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M181" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N181" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O181" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P181" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R181" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S181" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T181" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U181" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V181" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W181" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X181" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA181" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB181" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC181" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD181" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE181" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF181" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG181" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH181" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI181" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ181" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK181" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL181" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM181" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN181" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO181" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP181" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ181" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR181" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS181" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT181" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU181" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV181" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW181" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX181" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY181" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ181" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA181" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB181" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC181" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD181" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE181" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF181" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG181" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH181" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI181" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ181" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK181" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL181" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM181" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN181" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO181" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP181" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ181" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR181" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="182">
@@ -39402,211 +39402,211 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L182" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O182" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P182" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R182" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S182" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T182" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U182" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V182" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W182" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X182" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA182" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB182" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC182" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD182" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE182" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF182" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG182" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH182" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI182" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ182" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK182" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL182" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM182" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN182" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO182" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP182" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ182" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR182" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS182" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT182" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU182" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV182" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW182" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX182" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY182" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ182" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA182" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB182" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC182" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD182" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE182" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF182" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG182" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH182" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI182" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ182" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK182" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL182" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM182" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN182" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO182" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP182" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ182" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR182" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="183">
@@ -39616,211 +39616,211 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C183" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K183" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L183" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M183" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N183" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O183" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P183" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q183" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R183" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S183" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T183" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U183" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V183" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W183" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X183" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA183" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB183" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC183" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD183" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE183" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF183" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG183" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH183" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI183" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ183" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK183" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL183" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM183" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN183" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO183" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP183" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ183" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR183" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS183" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT183" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU183" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV183" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW183" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX183" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY183" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ183" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA183" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB183" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC183" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD183" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE183" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF183" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG183" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH183" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI183" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ183" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK183" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL183" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM183" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN183" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO183" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP183" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ183" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR183" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
     <row r="184">
@@ -39830,211 +39830,211 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>2.504</v>
+        <v>2.597</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>2.3035</v>
+        <v>2.411</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.7745</v>
+        <v>2.919</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>2.323</v>
+        <v>2.389</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6585</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.18</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>2.1155</v>
+        <v>2.1855</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="J184" s="3" t="n">
-        <v>2.292</v>
+        <v>2.371</v>
       </c>
       <c r="K184" s="3" t="n">
-        <v>1.486</v>
+        <v>1.466</v>
       </c>
       <c r="L184" s="3" t="n">
-        <v>1.5925</v>
+        <v>1.662</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>2.245</v>
+        <v>2.3045</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>2.282</v>
+        <v>2.3395</v>
       </c>
       <c r="O184" s="3" t="n">
-        <v>3.597</v>
+        <v>3.758</v>
       </c>
       <c r="P184" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.119</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.769</v>
       </c>
       <c r="R184" s="3" t="n">
-        <v>2.5585</v>
+        <v>2.6785</v>
       </c>
       <c r="S184" s="3" t="n">
-        <v>2.8575</v>
+        <v>2.9145</v>
       </c>
       <c r="T184" s="3" t="n">
-        <v>2.171</v>
+        <v>2.2785</v>
       </c>
       <c r="U184" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="V184" s="3" t="n">
-        <v>2.2025</v>
+        <v>2.269</v>
       </c>
       <c r="W184" s="3" t="n">
-        <v>1.9135</v>
+        <v>1.7885</v>
       </c>
       <c r="X184" s="3" t="n">
-        <v>2.213</v>
+        <v>2.2675</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>2.099</v>
+        <v>2.2065</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>2.207</v>
+        <v>2.276</v>
       </c>
       <c r="AA184" s="3" t="n">
-        <v>2.285</v>
+        <v>2.38</v>
       </c>
       <c r="AB184" s="3" t="n">
-        <v>2.299</v>
+        <v>2.367</v>
       </c>
       <c r="AC184" s="3" t="n">
-        <v>2.4835</v>
+        <v>2.5045</v>
       </c>
       <c r="AD184" s="3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE184" s="3" t="n">
-        <v>2.098</v>
+        <v>2.149</v>
       </c>
       <c r="AF184" s="3" t="n">
-        <v>3.4875</v>
+        <v>3.535</v>
       </c>
       <c r="AG184" s="3" t="n">
-        <v>2.5875</v>
+        <v>2.616</v>
       </c>
       <c r="AH184" s="3" t="n">
-        <v>2.098</v>
+        <v>2.163</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>1.594</v>
+        <v>1.534</v>
       </c>
       <c r="AJ184" s="3" t="n">
-        <v>2.569</v>
+        <v>2.669</v>
       </c>
       <c r="AK184" s="3" t="n">
-        <v>2.2385</v>
+        <v>2.3115</v>
       </c>
       <c r="AL184" s="3" t="n">
-        <v>1.9045</v>
+        <v>1.972</v>
       </c>
       <c r="AM184" s="3" t="n">
-        <v>2.7495</v>
+        <v>2.7625</v>
       </c>
       <c r="AN184" s="3" t="n">
-        <v>3.6195</v>
+        <v>3.627</v>
       </c>
       <c r="AO184" s="3" t="n">
-        <v>3.379</v>
+        <v>3.4325</v>
       </c>
       <c r="AP184" s="3" t="n">
-        <v>2.195</v>
+        <v>2.28</v>
       </c>
       <c r="AQ184" s="3" t="n">
-        <v>1.6925</v>
+        <v>1.787</v>
       </c>
       <c r="AR184" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5195</v>
       </c>
       <c r="AS184" s="3" t="n">
-        <v>1.583</v>
+        <v>1.6695</v>
       </c>
       <c r="AT184" s="3" t="n">
-        <v>1.7345</v>
+        <v>1.827</v>
       </c>
       <c r="AU184" s="3" t="n">
-        <v>2.1015</v>
+        <v>2.209</v>
       </c>
       <c r="AV184" s="3" t="n">
-        <v>2.497</v>
+        <v>2.562</v>
       </c>
       <c r="AW184" s="3" t="n">
-        <v>3.407</v>
+        <v>3.5155</v>
       </c>
       <c r="AX184" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.55</v>
       </c>
       <c r="AY184" s="3" t="n">
-        <v>2</v>
+        <v>2.1065</v>
       </c>
       <c r="AZ184" s="3" t="n">
-        <v>2.339</v>
+        <v>2.459</v>
       </c>
       <c r="BA184" s="3" t="n">
-        <v>1.7825</v>
+        <v>1.8975</v>
       </c>
       <c r="BB184" s="3" t="n">
-        <v>1.629</v>
+        <v>1.696</v>
       </c>
       <c r="BC184" s="3" t="n">
-        <v>3.001</v>
+        <v>3.121</v>
       </c>
       <c r="BD184" s="3" t="n">
-        <v>2.7635</v>
+        <v>2.8835</v>
       </c>
       <c r="BE184" s="3" t="n">
-        <v>2.347</v>
+        <v>2.432</v>
       </c>
       <c r="BF184" s="3" t="n">
-        <v>1.884</v>
+        <v>2.0115</v>
       </c>
       <c r="BG184" s="3" t="n">
-        <v>2.116</v>
+        <v>2.236</v>
       </c>
       <c r="BH184" s="3" t="n">
-        <v>2.552</v>
+        <v>2.6745</v>
       </c>
       <c r="BI184" s="3" t="n">
-        <v>3.267</v>
+        <v>3.387</v>
       </c>
       <c r="BJ184" s="3" t="n">
-        <v>3.315</v>
+        <v>3.387</v>
       </c>
       <c r="BK184" s="3" t="n">
-        <v>1.64</v>
+        <v>1.697</v>
       </c>
       <c r="BL184" s="3" t="n">
-        <v>2.9185</v>
+        <v>3.0385</v>
       </c>
       <c r="BM184" s="3" t="n">
-        <v>2.456</v>
+        <v>2.9335</v>
       </c>
       <c r="BN184" s="3" t="n">
-        <v>3.464</v>
+        <v>3.564</v>
       </c>
       <c r="BO184" s="3" t="n">
-        <v>1.7545</v>
+        <v>1.822</v>
       </c>
       <c r="BP184" s="3" t="n">
-        <v>1.852</v>
+        <v>1.9495</v>
       </c>
       <c r="BQ184" s="3" t="n">
-        <v>2.275</v>
+        <v>2.405</v>
       </c>
       <c r="BR184" s="3" t="n">
-        <v>1.5685</v>
+        <v>1.5575</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -32982,16 +32982,16 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>2.5626</v>
+        <v>2.565</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>2.2769</v>
+        <v>2.275</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>1.75</v>
+        <v>1.745</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>2.4184</v>
+        <v>2.42</v>
       </c>
       <c r="F152" s="3" t="n">
         <v>2.58</v>
@@ -33000,193 +33000,193 @@
         <v>2.3</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>2.2737</v>
+        <v>2.275</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>2.4471</v>
+        <v>2.445</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>2.4001</v>
+        <v>2.4</v>
       </c>
       <c r="K152" s="3" t="n">
-        <v>1.497</v>
+        <v>1.5</v>
       </c>
       <c r="L152" s="3" t="n">
-        <v>1.5188</v>
+        <v>1.52</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>2.4436</v>
+        <v>2.435</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>2.385</v>
+        <v>2.415</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>3.6644</v>
+        <v>3.81</v>
       </c>
       <c r="P152" s="3" t="n">
-        <v>2.1305</v>
+        <v>2.13</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>2.8491</v>
+        <v>2.85</v>
       </c>
       <c r="R152" s="3" t="n">
-        <v>2.351</v>
+        <v>2.345</v>
       </c>
       <c r="S152" s="3" t="n">
-        <v>2.4129</v>
+        <v>2.375</v>
       </c>
       <c r="T152" s="3" t="n">
-        <v>2.1642</v>
+        <v>2.165</v>
       </c>
       <c r="U152" s="3" t="n">
-        <v>2.666</v>
+        <v>2.78</v>
       </c>
       <c r="V152" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="W152" s="3" t="n">
-        <v>1.4417</v>
+        <v>1.44</v>
       </c>
       <c r="X152" s="3" t="n">
-        <v>2.3483</v>
+        <v>2.35</v>
       </c>
       <c r="Y152" s="3" t="n">
-        <v>2.1424</v>
+        <v>2.145</v>
       </c>
       <c r="Z152" s="3" t="n">
-        <v>2.3876</v>
+        <v>2.39</v>
       </c>
       <c r="AA152" s="3" t="n">
-        <v>2.4044</v>
+        <v>2.405</v>
       </c>
       <c r="AB152" s="3" t="n">
-        <v>2.4013</v>
+        <v>2.4</v>
       </c>
       <c r="AC152" s="3" t="n">
-        <v>2.3448</v>
+        <v>2.64</v>
       </c>
       <c r="AD152" s="3" t="n">
-        <v>2.5775</v>
+        <v>2.8</v>
       </c>
       <c r="AE152" s="3" t="n">
-        <v>2.1143</v>
+        <v>2.115</v>
       </c>
       <c r="AF152" s="3" t="n">
-        <v>3.6489</v>
+        <v>3.65</v>
       </c>
       <c r="AG152" s="3" t="n">
-        <v>2.8022</v>
+        <v>2.805</v>
       </c>
       <c r="AH152" s="3" t="n">
-        <v>2.2451</v>
+        <v>2.245</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>1.4992</v>
+        <v>1.5</v>
       </c>
       <c r="AJ152" s="3" t="n">
-        <v>2.5471</v>
+        <v>2.545</v>
       </c>
       <c r="AK152" s="3" t="n">
-        <v>2.3927</v>
+        <v>2.395</v>
       </c>
       <c r="AL152" s="3" t="n">
-        <v>2.304</v>
+        <v>2.305</v>
       </c>
       <c r="AM152" s="3" t="n">
-        <v>2.7194</v>
+        <v>2.725</v>
       </c>
       <c r="AN152" s="3" t="n">
-        <v>3.6749</v>
+        <v>3.675</v>
       </c>
       <c r="AO152" s="3" t="n">
-        <v>3.5681</v>
+        <v>3.57</v>
       </c>
       <c r="AP152" s="3" t="n">
-        <v>2.2911</v>
+        <v>2.29</v>
       </c>
       <c r="AQ152" s="3" t="n">
-        <v>1.5885</v>
+        <v>1.59</v>
       </c>
       <c r="AR152" s="3" t="n">
-        <v>2.4352</v>
+        <v>2.435</v>
       </c>
       <c r="AS152" s="3" t="n">
-        <v>1.476</v>
+        <v>1.475</v>
       </c>
       <c r="AT152" s="3" t="n">
-        <v>1.5269</v>
+        <v>1.525</v>
       </c>
       <c r="AU152" s="3" t="n">
-        <v>2.1514</v>
+        <v>2.15</v>
       </c>
       <c r="AV152" s="3" t="n">
-        <v>2.5364</v>
+        <v>2.535</v>
       </c>
       <c r="AW152" s="3" t="n">
-        <v>3.6049</v>
+        <v>3.605</v>
       </c>
       <c r="AX152" s="3" t="n">
-        <v>2.4512</v>
+        <v>2.45</v>
       </c>
       <c r="AY152" s="3" t="n">
-        <v>2.1425</v>
+        <v>2.145</v>
       </c>
       <c r="AZ152" s="3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BA152" s="3" t="n">
-        <v>1.7248</v>
+        <v>1.73</v>
       </c>
       <c r="BB152" s="3" t="n">
-        <v>1.4214</v>
+        <v>1.42</v>
       </c>
       <c r="BC152" s="3" t="n">
-        <v>1.95</v>
+        <v>1.995</v>
       </c>
       <c r="BD152" s="3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BE152" s="3" t="n">
-        <v>2.4289</v>
+        <v>2.43</v>
       </c>
       <c r="BF152" s="3" t="n">
-        <v>1.5269</v>
+        <v>1.58</v>
       </c>
       <c r="BG152" s="3" t="n">
-        <v>2.1473</v>
+        <v>2.145</v>
       </c>
       <c r="BH152" s="3" t="n">
-        <v>2.4492</v>
+        <v>2.45</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>3.4973</v>
+        <v>3.495</v>
       </c>
       <c r="BJ152" s="3" t="n">
-        <v>3.5144</v>
+        <v>3.515</v>
       </c>
       <c r="BK152" s="3" t="n">
-        <v>1.4694</v>
+        <v>1.47</v>
       </c>
       <c r="BL152" s="3" t="n">
-        <v>3.5144</v>
+        <v>3.085</v>
       </c>
       <c r="BM152" s="3" t="n">
-        <v>3.514</v>
+        <v>2.345</v>
       </c>
       <c r="BN152" s="3" t="n">
-        <v>3.514</v>
+        <v>3.515</v>
       </c>
       <c r="BO152" s="3" t="n">
-        <v>1.4769</v>
+        <v>1.485</v>
       </c>
       <c r="BP152" s="3" t="n">
         <v>1.55</v>
       </c>
       <c r="BQ152" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.41</v>
       </c>
       <c r="BR152" s="3" t="n">
-        <v>1.4987</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="153">
@@ -33196,211 +33196,211 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>2.626</v>
+        <v>2.5129</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>2.198</v>
+        <v>2.2411</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2.363</v>
+        <v>2.3218</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2.636</v>
+        <v>2.4706</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2.16</v>
+        <v>2.2164</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>2.16</v>
+        <v>2.2179</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>2.249</v>
+        <v>2.3431</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>2.199</v>
+        <v>2.3066</v>
       </c>
       <c r="K153" s="3" t="n">
-        <v>1.539</v>
+        <v>1.3453</v>
       </c>
       <c r="L153" s="3" t="n">
-        <v>1.4495</v>
+        <v>1.2365</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>2.2775</v>
+        <v>2.2632</v>
       </c>
       <c r="N153" s="3" t="n">
-        <v>2.42</v>
+        <v>2.325</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>3.7025</v>
+        <v>3.3634</v>
       </c>
       <c r="P153" s="3" t="n">
-        <v>2.2005</v>
+        <v>2.0119</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>2.805</v>
+        <v>2.667</v>
       </c>
       <c r="R153" s="3" t="n">
-        <v>1.898</v>
+        <v>2.2573</v>
       </c>
       <c r="S153" s="3" t="n">
-        <v>2.07</v>
+        <v>2.3143</v>
       </c>
       <c r="T153" s="3" t="n">
-        <v>2.265</v>
+        <v>2.0671</v>
       </c>
       <c r="U153" s="3" t="n">
-        <v>3.106</v>
+        <v>2.6</v>
       </c>
       <c r="V153" s="3" t="n">
-        <v>2.305</v>
+        <v>2.3305</v>
       </c>
       <c r="W153" s="3" t="n">
-        <v>1.5495</v>
+        <v>1.3227</v>
       </c>
       <c r="X153" s="3" t="n">
-        <v>2.295</v>
+        <v>2.3053</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>2.291</v>
+        <v>2.0113</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>2.3</v>
+        <v>2.3254</v>
       </c>
       <c r="AA153" s="3" t="n">
-        <v>2.204</v>
+        <v>2.298</v>
       </c>
       <c r="AB153" s="3" t="n">
-        <v>2.239</v>
+        <v>2.2965</v>
       </c>
       <c r="AC153" s="3" t="n">
-        <v>2.635</v>
+        <v>2.2153</v>
       </c>
       <c r="AD153" s="3" t="n">
-        <v>2.5775</v>
+        <v>2.45</v>
       </c>
       <c r="AE153" s="3" t="n">
-        <v>2.0575</v>
+        <v>2.2356</v>
       </c>
       <c r="AF153" s="3" t="n">
-        <v>3.632</v>
+        <v>3.6106</v>
       </c>
       <c r="AG153" s="3" t="n">
-        <v>2.6405</v>
+        <v>2.6998</v>
       </c>
       <c r="AH153" s="3" t="n">
-        <v>2.135</v>
+        <v>2.1737</v>
       </c>
       <c r="AI153" s="3" t="n">
-        <v>1.6</v>
+        <v>1.3354</v>
       </c>
       <c r="AJ153" s="3" t="n">
-        <v>2.656</v>
+        <v>2.4964</v>
       </c>
       <c r="AK153" s="3" t="n">
-        <v>2.155</v>
+        <v>2.26</v>
       </c>
       <c r="AL153" s="3" t="n">
-        <v>2.144</v>
+        <v>1.9808</v>
       </c>
       <c r="AM153" s="3" t="n">
-        <v>3.031</v>
+        <v>2.6219</v>
       </c>
       <c r="AN153" s="3" t="n">
-        <v>4.142</v>
+        <v>3.6325</v>
       </c>
       <c r="AO153" s="3" t="n">
-        <v>3.18</v>
+        <v>3.388</v>
       </c>
       <c r="AP153" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.25</v>
       </c>
       <c r="AQ153" s="3" t="n">
-        <v>1.577</v>
+        <v>1.2537</v>
       </c>
       <c r="AR153" s="3" t="n">
-        <v>2.3775</v>
+        <v>2.3024</v>
       </c>
       <c r="AS153" s="3" t="n">
-        <v>0.991</v>
+        <v>1.2027</v>
       </c>
       <c r="AT153" s="3" t="n">
-        <v>1.5905</v>
+        <v>1.3344</v>
       </c>
       <c r="AU153" s="3" t="n">
-        <v>2.256</v>
+        <v>2.041</v>
       </c>
       <c r="AV153" s="3" t="n">
-        <v>2.5775</v>
+        <v>2.4382</v>
       </c>
       <c r="AW153" s="3" t="n">
-        <v>3.405</v>
+        <v>3.5022</v>
       </c>
       <c r="AX153" s="3" t="n">
-        <v>2.3775</v>
+        <v>2.4308</v>
       </c>
       <c r="AY153" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.013</v>
       </c>
       <c r="AZ153" s="3" t="n">
-        <v>2.3005</v>
+        <v>1.9834</v>
       </c>
       <c r="BA153" s="3" t="n">
-        <v>1.4285</v>
+        <v>1.4894</v>
       </c>
       <c r="BB153" s="3" t="n">
-        <v>1.4095</v>
+        <v>1.2904</v>
       </c>
       <c r="BC153" s="3" t="n">
-        <v>1.5605</v>
+        <v>1.77</v>
       </c>
       <c r="BD153" s="3" t="n">
-        <v>1.4605</v>
+        <v>1.57</v>
       </c>
       <c r="BE153" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.3216</v>
       </c>
       <c r="BF153" s="3" t="n">
-        <v>1.6305</v>
+        <v>1.3344</v>
       </c>
       <c r="BG153" s="3" t="n">
-        <v>2.2465</v>
+        <v>2.0059</v>
       </c>
       <c r="BH153" s="3" t="n">
-        <v>2.4895</v>
+        <v>2.3617</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>3.1805</v>
+        <v>3.2284</v>
       </c>
       <c r="BJ153" s="3" t="n">
-        <v>3.2055</v>
+        <v>3.2134</v>
       </c>
       <c r="BK153" s="3" t="n">
-        <v>1.1475</v>
+        <v>1.3002</v>
       </c>
       <c r="BL153" s="3" t="n">
-        <v>3.0245</v>
+        <v>3.2134</v>
       </c>
       <c r="BM153" s="3" t="n">
-        <v>2.271</v>
+        <v>3.1938</v>
       </c>
       <c r="BN153" s="3" t="n">
-        <v>3.405</v>
+        <v>3.1938</v>
       </c>
       <c r="BO153" s="3" t="n">
-        <v>1.58</v>
+        <v>1.2844</v>
       </c>
       <c r="BP153" s="3" t="n">
-        <v>1.5675</v>
+        <v>1.4214</v>
       </c>
       <c r="BQ153" s="3" t="n">
-        <v>2.2275</v>
+        <v>2.2889</v>
       </c>
       <c r="BR153" s="3" t="n">
-        <v>1.49</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="154">
@@ -33410,211 +33410,211 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>2.626</v>
+        <v>2.5129</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2.198</v>
+        <v>2.2411</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2.363</v>
+        <v>2.3218</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2.636</v>
+        <v>2.4706</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2.16</v>
+        <v>2.2164</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>2.16</v>
+        <v>2.2179</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>2.249</v>
+        <v>2.3431</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>2.199</v>
+        <v>2.3066</v>
       </c>
       <c r="K154" s="3" t="n">
-        <v>1.539</v>
+        <v>1.3453</v>
       </c>
       <c r="L154" s="3" t="n">
-        <v>1.4495</v>
+        <v>1.2365</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>2.2775</v>
+        <v>2.2632</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>2.42</v>
+        <v>2.325</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>3.7025</v>
+        <v>3.3634</v>
       </c>
       <c r="P154" s="3" t="n">
-        <v>2.2005</v>
+        <v>2.0119</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>2.805</v>
+        <v>2.667</v>
       </c>
       <c r="R154" s="3" t="n">
-        <v>1.898</v>
+        <v>2.2573</v>
       </c>
       <c r="S154" s="3" t="n">
-        <v>2.07</v>
+        <v>2.3143</v>
       </c>
       <c r="T154" s="3" t="n">
-        <v>2.265</v>
+        <v>2.0671</v>
       </c>
       <c r="U154" s="3" t="n">
-        <v>3.106</v>
+        <v>2.6</v>
       </c>
       <c r="V154" s="3" t="n">
-        <v>2.305</v>
+        <v>2.3305</v>
       </c>
       <c r="W154" s="3" t="n">
-        <v>1.5495</v>
+        <v>1.3227</v>
       </c>
       <c r="X154" s="3" t="n">
-        <v>2.295</v>
+        <v>2.3053</v>
       </c>
       <c r="Y154" s="3" t="n">
-        <v>2.291</v>
+        <v>2.0113</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>2.3</v>
+        <v>2.3254</v>
       </c>
       <c r="AA154" s="3" t="n">
-        <v>2.204</v>
+        <v>2.298</v>
       </c>
       <c r="AB154" s="3" t="n">
-        <v>2.239</v>
+        <v>2.2965</v>
       </c>
       <c r="AC154" s="3" t="n">
-        <v>2.635</v>
+        <v>2.2153</v>
       </c>
       <c r="AD154" s="3" t="n">
-        <v>2.5775</v>
+        <v>2.45</v>
       </c>
       <c r="AE154" s="3" t="n">
-        <v>2.0575</v>
+        <v>2.2356</v>
       </c>
       <c r="AF154" s="3" t="n">
-        <v>3.632</v>
+        <v>3.6106</v>
       </c>
       <c r="AG154" s="3" t="n">
-        <v>2.6405</v>
+        <v>2.6998</v>
       </c>
       <c r="AH154" s="3" t="n">
-        <v>2.135</v>
+        <v>2.1737</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>1.6</v>
+        <v>1.3354</v>
       </c>
       <c r="AJ154" s="3" t="n">
-        <v>2.656</v>
+        <v>2.4964</v>
       </c>
       <c r="AK154" s="3" t="n">
-        <v>2.155</v>
+        <v>2.26</v>
       </c>
       <c r="AL154" s="3" t="n">
-        <v>2.144</v>
+        <v>1.9808</v>
       </c>
       <c r="AM154" s="3" t="n">
-        <v>3.031</v>
+        <v>2.6219</v>
       </c>
       <c r="AN154" s="3" t="n">
-        <v>4.142</v>
+        <v>3.6325</v>
       </c>
       <c r="AO154" s="3" t="n">
-        <v>3.18</v>
+        <v>3.388</v>
       </c>
       <c r="AP154" s="3" t="n">
-        <v>2.0775</v>
+        <v>2.25</v>
       </c>
       <c r="AQ154" s="3" t="n">
-        <v>1.577</v>
+        <v>1.2537</v>
       </c>
       <c r="AR154" s="3" t="n">
-        <v>2.3775</v>
+        <v>2.3024</v>
       </c>
       <c r="AS154" s="3" t="n">
-        <v>0.991</v>
+        <v>1.2027</v>
       </c>
       <c r="AT154" s="3" t="n">
-        <v>1.5905</v>
+        <v>1.3344</v>
       </c>
       <c r="AU154" s="3" t="n">
-        <v>2.256</v>
+        <v>2.041</v>
       </c>
       <c r="AV154" s="3" t="n">
-        <v>2.5775</v>
+        <v>2.4382</v>
       </c>
       <c r="AW154" s="3" t="n">
-        <v>3.405</v>
+        <v>3.5022</v>
       </c>
       <c r="AX154" s="3" t="n">
-        <v>2.3775</v>
+        <v>2.4308</v>
       </c>
       <c r="AY154" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.013</v>
       </c>
       <c r="AZ154" s="3" t="n">
-        <v>2.3005</v>
+        <v>1.9834</v>
       </c>
       <c r="BA154" s="3" t="n">
-        <v>1.4285</v>
+        <v>1.4894</v>
       </c>
       <c r="BB154" s="3" t="n">
-        <v>1.4095</v>
+        <v>1.2904</v>
       </c>
       <c r="BC154" s="3" t="n">
-        <v>1.5605</v>
+        <v>1.77</v>
       </c>
       <c r="BD154" s="3" t="n">
-        <v>1.4605</v>
+        <v>1.57</v>
       </c>
       <c r="BE154" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.3216</v>
       </c>
       <c r="BF154" s="3" t="n">
-        <v>1.6305</v>
+        <v>1.3344</v>
       </c>
       <c r="BG154" s="3" t="n">
-        <v>2.2465</v>
+        <v>2.0059</v>
       </c>
       <c r="BH154" s="3" t="n">
-        <v>2.4895</v>
+        <v>2.3617</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>3.1805</v>
+        <v>3.2284</v>
       </c>
       <c r="BJ154" s="3" t="n">
-        <v>3.2055</v>
+        <v>3.2134</v>
       </c>
       <c r="BK154" s="3" t="n">
-        <v>1.1475</v>
+        <v>1.3002</v>
       </c>
       <c r="BL154" s="3" t="n">
-        <v>3.0245</v>
+        <v>3.2134</v>
       </c>
       <c r="BM154" s="3" t="n">
-        <v>2.271</v>
+        <v>3.1938</v>
       </c>
       <c r="BN154" s="3" t="n">
-        <v>3.405</v>
+        <v>3.1938</v>
       </c>
       <c r="BO154" s="3" t="n">
-        <v>1.58</v>
+        <v>1.2844</v>
       </c>
       <c r="BP154" s="3" t="n">
-        <v>1.5675</v>
+        <v>1.4214</v>
       </c>
       <c r="BQ154" s="3" t="n">
-        <v>2.2275</v>
+        <v>2.2889</v>
       </c>
       <c r="BR154" s="3" t="n">
-        <v>1.49</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="155">
@@ -33624,211 +33624,211 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K155" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L155" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P155" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R155" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S155" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T155" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U155" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V155" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W155" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X155" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA155" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB155" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC155" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD155" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE155" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF155" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG155" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH155" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ155" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK155" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL155" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM155" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN155" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO155" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP155" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ155" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR155" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS155" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT155" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU155" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV155" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW155" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX155" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY155" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ155" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA155" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB155" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC155" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD155" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE155" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF155" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG155" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH155" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI155" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ155" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK155" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL155" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM155" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN155" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO155" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP155" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ155" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR155" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="156">
@@ -33838,211 +33838,211 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K156" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L156" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P156" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R156" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S156" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T156" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U156" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V156" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W156" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X156" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA156" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB156" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC156" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD156" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE156" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF156" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG156" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH156" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ156" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK156" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL156" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM156" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN156" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO156" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP156" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ156" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR156" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS156" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT156" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU156" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV156" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW156" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX156" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY156" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ156" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA156" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB156" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC156" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD156" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE156" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF156" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG156" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH156" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI156" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ156" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK156" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL156" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM156" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN156" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO156" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP156" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ156" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR156" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="157">
@@ -34052,211 +34052,211 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K157" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L157" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P157" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R157" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S157" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T157" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U157" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V157" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W157" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X157" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA157" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB157" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC157" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD157" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE157" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF157" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG157" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH157" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ157" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK157" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL157" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM157" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN157" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO157" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP157" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ157" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR157" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS157" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT157" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU157" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV157" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW157" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX157" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY157" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ157" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA157" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB157" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC157" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD157" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE157" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF157" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG157" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH157" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI157" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ157" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK157" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL157" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM157" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN157" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO157" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP157" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ157" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR157" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="158">
@@ -34266,211 +34266,211 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K158" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L158" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O158" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P158" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R158" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S158" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T158" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U158" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V158" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W158" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X158" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA158" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB158" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC158" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD158" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE158" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF158" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG158" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH158" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ158" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK158" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL158" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM158" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN158" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO158" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP158" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ158" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR158" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS158" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT158" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU158" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV158" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW158" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX158" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY158" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ158" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA158" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB158" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC158" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD158" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE158" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF158" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG158" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH158" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI158" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ158" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK158" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL158" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM158" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN158" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO158" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP158" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ158" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR158" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="159">
@@ -34480,211 +34480,211 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C159" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K159" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L159" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P159" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R159" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S159" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T159" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U159" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V159" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W159" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X159" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA159" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB159" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC159" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD159" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE159" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF159" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG159" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH159" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ159" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK159" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL159" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM159" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN159" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO159" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP159" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ159" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR159" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS159" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT159" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU159" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV159" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW159" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX159" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY159" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ159" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA159" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB159" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC159" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD159" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE159" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF159" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG159" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH159" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI159" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ159" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK159" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL159" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM159" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN159" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO159" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP159" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ159" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR159" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="160">
@@ -34694,211 +34694,211 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K160" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L160" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P160" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R160" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S160" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T160" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U160" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V160" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W160" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X160" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA160" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB160" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC160" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD160" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE160" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF160" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG160" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH160" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ160" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK160" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL160" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM160" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN160" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO160" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP160" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ160" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR160" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS160" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT160" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU160" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV160" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW160" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX160" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY160" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ160" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA160" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB160" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC160" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD160" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE160" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF160" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG160" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH160" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI160" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ160" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK160" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL160" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM160" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN160" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO160" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP160" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ160" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR160" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="161">
@@ -34908,211 +34908,211 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C161" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K161" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L161" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M161" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P161" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q161" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R161" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S161" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T161" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U161" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V161" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W161" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X161" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA161" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB161" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC161" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD161" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE161" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF161" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG161" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH161" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ161" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK161" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL161" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM161" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN161" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO161" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP161" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ161" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR161" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS161" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT161" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU161" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV161" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW161" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX161" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY161" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ161" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA161" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB161" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC161" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD161" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE161" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF161" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG161" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH161" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI161" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ161" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK161" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL161" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM161" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN161" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO161" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP161" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ161" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR161" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="162">
@@ -35122,211 +35122,211 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K162" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P162" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R162" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S162" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T162" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U162" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V162" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W162" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X162" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA162" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB162" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC162" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD162" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE162" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF162" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG162" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH162" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ162" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK162" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL162" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM162" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN162" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO162" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP162" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ162" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR162" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS162" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT162" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU162" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV162" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW162" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX162" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY162" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ162" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA162" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB162" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC162" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD162" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE162" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF162" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG162" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH162" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI162" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ162" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK162" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL162" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM162" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN162" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO162" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP162" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ162" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR162" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="163">
@@ -35336,211 +35336,211 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K163" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L163" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O163" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P163" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R163" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S163" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T163" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U163" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V163" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W163" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X163" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA163" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB163" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC163" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD163" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE163" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF163" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG163" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH163" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ163" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK163" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL163" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM163" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN163" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO163" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP163" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ163" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR163" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS163" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT163" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU163" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV163" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW163" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX163" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY163" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ163" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA163" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB163" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC163" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD163" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE163" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF163" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG163" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH163" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI163" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ163" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK163" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL163" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM163" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN163" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO163" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP163" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ163" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR163" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="164">
@@ -35550,211 +35550,211 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K164" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L164" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O164" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P164" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R164" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S164" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T164" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U164" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V164" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W164" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X164" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y164" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA164" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB164" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC164" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD164" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE164" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF164" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG164" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH164" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI164" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ164" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM164" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN164" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO164" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP164" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ164" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR164" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS164" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT164" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU164" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV164" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW164" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX164" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY164" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ164" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA164" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB164" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC164" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD164" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE164" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF164" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG164" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH164" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI164" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ164" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK164" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL164" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM164" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN164" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO164" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP164" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ164" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR164" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="165">
@@ -35764,211 +35764,211 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K165" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L165" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N165" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O165" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P165" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R165" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S165" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T165" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U165" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V165" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W165" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X165" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA165" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB165" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC165" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD165" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE165" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF165" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG165" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH165" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI165" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ165" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK165" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL165" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM165" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN165" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO165" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP165" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ165" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR165" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS165" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT165" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU165" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV165" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW165" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX165" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY165" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ165" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA165" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB165" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC165" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD165" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE165" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF165" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG165" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH165" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI165" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ165" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK165" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL165" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM165" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN165" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO165" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP165" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ165" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR165" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="166">
@@ -35978,211 +35978,211 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K166" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N166" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P166" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R166" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S166" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T166" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U166" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V166" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W166" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X166" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA166" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB166" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC166" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD166" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE166" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF166" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG166" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH166" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI166" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ166" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK166" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL166" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM166" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN166" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO166" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP166" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ166" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR166" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS166" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT166" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU166" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV166" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW166" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX166" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY166" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ166" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA166" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB166" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC166" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD166" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE166" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF166" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG166" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH166" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI166" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ166" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK166" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL166" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM166" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN166" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO166" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP166" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ166" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR166" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="167">
@@ -36192,211 +36192,211 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C167" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K167" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P167" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R167" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S167" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T167" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U167" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V167" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W167" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X167" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA167" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC167" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD167" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE167" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF167" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG167" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH167" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ167" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM167" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN167" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO167" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP167" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ167" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR167" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS167" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT167" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU167" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV167" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW167" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX167" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY167" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ167" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA167" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB167" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC167" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD167" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE167" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF167" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG167" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH167" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI167" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ167" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK167" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL167" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM167" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN167" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO167" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP167" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ167" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR167" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="168">
@@ -36406,211 +36406,211 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K168" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L168" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N168" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O168" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P168" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R168" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S168" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T168" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U168" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V168" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W168" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X168" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA168" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC168" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD168" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE168" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF168" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG168" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH168" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ168" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM168" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN168" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO168" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP168" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ168" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR168" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS168" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT168" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU168" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV168" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW168" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX168" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY168" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ168" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA168" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB168" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC168" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD168" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE168" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF168" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG168" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH168" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI168" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ168" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK168" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL168" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM168" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN168" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO168" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP168" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ168" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR168" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="169">
@@ -36620,211 +36620,211 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K169" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L169" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O169" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P169" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R169" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S169" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T169" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U169" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V169" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W169" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X169" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA169" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB169" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC169" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD169" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE169" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF169" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG169" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH169" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ169" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK169" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM169" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN169" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO169" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP169" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ169" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR169" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS169" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT169" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU169" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV169" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW169" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX169" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY169" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ169" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA169" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB169" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC169" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD169" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE169" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF169" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG169" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH169" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI169" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ169" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK169" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL169" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM169" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN169" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO169" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP169" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ169" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR169" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="170">
@@ -36834,211 +36834,211 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K170" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L170" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O170" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P170" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R170" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S170" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T170" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U170" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V170" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W170" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X170" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA170" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB170" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC170" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD170" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE170" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF170" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG170" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH170" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI170" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ170" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK170" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL170" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM170" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN170" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO170" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP170" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ170" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR170" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS170" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT170" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU170" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV170" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW170" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX170" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY170" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ170" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA170" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB170" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC170" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD170" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE170" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF170" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG170" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH170" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI170" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ170" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK170" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL170" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM170" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN170" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO170" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP170" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ170" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR170" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="171">
@@ -37048,211 +37048,211 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C171" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K171" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L171" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M171" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N171" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P171" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R171" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S171" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T171" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U171" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V171" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W171" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X171" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA171" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB171" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC171" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD171" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE171" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF171" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG171" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH171" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI171" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ171" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK171" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL171" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM171" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN171" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO171" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP171" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ171" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR171" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS171" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT171" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU171" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV171" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW171" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX171" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY171" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ171" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA171" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB171" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC171" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD171" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE171" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF171" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG171" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH171" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI171" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ171" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK171" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL171" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM171" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN171" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO171" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP171" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ171" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR171" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="172">
@@ -37262,211 +37262,211 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K172" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L172" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O172" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P172" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R172" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S172" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T172" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U172" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V172" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W172" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X172" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA172" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB172" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC172" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD172" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE172" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF172" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG172" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH172" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI172" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ172" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK172" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL172" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM172" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN172" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO172" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP172" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ172" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR172" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS172" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT172" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU172" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV172" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW172" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX172" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY172" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ172" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA172" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB172" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC172" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD172" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE172" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF172" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG172" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH172" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI172" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ172" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK172" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL172" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM172" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN172" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO172" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP172" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ172" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR172" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="173">
@@ -37476,211 +37476,211 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K173" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L173" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P173" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R173" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S173" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T173" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U173" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V173" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W173" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X173" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA173" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB173" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC173" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD173" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE173" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF173" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG173" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH173" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI173" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ173" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK173" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM173" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN173" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO173" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP173" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ173" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR173" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS173" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT173" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU173" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV173" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW173" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX173" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY173" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ173" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA173" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB173" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC173" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD173" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE173" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF173" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG173" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH173" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI173" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ173" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK173" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL173" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM173" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN173" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO173" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP173" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ173" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR173" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="174">
@@ -37690,211 +37690,211 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K174" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L174" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N174" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O174" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P174" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R174" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S174" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T174" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U174" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V174" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W174" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X174" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA174" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB174" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC174" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD174" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE174" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF174" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG174" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH174" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI174" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ174" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK174" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM174" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN174" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO174" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP174" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ174" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR174" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS174" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT174" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU174" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV174" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW174" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX174" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY174" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ174" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA174" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB174" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC174" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD174" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE174" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF174" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG174" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH174" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI174" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ174" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK174" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL174" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM174" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN174" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO174" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP174" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ174" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR174" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="175">
@@ -37904,211 +37904,211 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C175" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L175" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P175" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R175" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S175" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T175" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U175" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V175" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W175" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X175" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA175" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB175" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC175" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD175" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE175" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF175" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG175" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH175" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ175" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK175" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM175" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN175" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO175" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP175" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ175" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR175" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS175" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT175" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU175" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV175" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW175" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX175" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY175" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ175" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA175" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB175" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC175" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD175" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE175" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF175" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG175" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH175" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI175" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ175" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK175" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL175" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM175" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN175" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO175" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP175" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ175" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR175" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="176">
@@ -38118,211 +38118,211 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P176" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R176" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S176" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T176" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U176" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V176" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W176" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X176" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA176" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB176" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC176" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD176" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE176" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF176" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG176" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH176" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ176" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK176" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL176" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM176" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN176" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO176" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP176" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ176" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR176" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS176" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT176" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU176" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV176" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW176" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX176" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY176" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ176" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA176" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB176" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC176" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD176" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE176" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF176" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG176" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH176" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI176" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ176" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK176" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL176" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM176" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN176" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO176" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP176" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ176" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR176" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="177">
@@ -38332,211 +38332,211 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K177" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L177" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O177" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P177" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R177" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S177" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T177" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U177" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V177" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W177" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X177" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA177" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB177" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC177" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD177" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE177" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF177" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG177" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH177" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ177" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL177" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM177" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN177" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO177" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP177" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ177" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR177" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS177" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT177" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU177" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV177" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW177" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX177" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY177" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ177" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA177" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB177" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC177" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD177" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE177" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF177" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG177" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH177" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI177" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ177" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK177" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL177" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM177" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN177" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO177" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP177" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ177" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR177" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="178">
@@ -38546,211 +38546,211 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L178" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P178" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R178" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S178" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T178" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U178" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V178" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W178" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X178" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA178" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB178" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC178" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD178" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE178" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF178" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG178" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH178" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ178" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK178" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL178" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM178" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN178" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO178" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP178" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ178" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR178" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS178" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT178" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU178" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV178" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW178" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX178" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY178" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ178" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA178" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB178" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC178" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD178" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE178" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF178" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG178" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH178" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI178" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ178" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK178" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL178" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM178" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN178" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO178" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP178" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ178" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR178" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="179">
@@ -38760,211 +38760,211 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C179" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K179" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L179" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M179" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N179" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O179" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P179" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q179" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R179" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S179" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T179" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U179" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V179" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W179" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X179" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y179" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z179" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA179" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB179" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC179" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD179" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE179" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF179" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG179" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH179" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ179" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK179" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM179" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN179" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO179" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP179" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ179" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR179" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS179" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT179" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU179" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV179" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW179" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX179" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY179" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ179" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA179" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB179" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC179" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD179" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE179" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF179" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG179" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH179" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI179" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ179" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK179" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL179" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM179" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN179" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO179" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP179" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ179" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR179" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="180">
@@ -38974,211 +38974,211 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J180" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K180" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L180" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P180" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R180" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S180" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T180" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U180" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V180" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W180" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X180" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA180" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB180" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC180" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD180" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE180" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF180" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG180" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH180" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ180" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK180" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL180" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM180" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN180" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO180" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP180" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ180" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR180" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS180" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT180" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU180" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV180" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW180" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX180" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY180" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ180" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA180" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB180" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC180" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD180" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE180" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF180" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG180" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH180" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI180" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ180" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK180" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL180" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM180" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN180" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO180" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP180" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ180" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR180" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="181">
@@ -39188,211 +39188,211 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C181" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K181" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L181" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M181" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N181" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O181" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P181" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R181" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S181" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T181" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U181" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V181" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W181" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X181" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA181" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB181" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC181" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD181" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE181" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF181" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG181" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH181" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI181" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ181" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK181" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL181" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM181" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN181" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO181" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP181" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ181" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR181" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS181" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT181" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU181" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV181" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW181" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX181" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY181" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ181" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA181" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB181" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC181" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD181" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE181" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF181" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG181" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH181" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI181" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ181" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK181" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL181" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM181" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN181" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO181" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP181" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ181" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR181" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="182">
@@ -39402,211 +39402,211 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J182" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L182" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O182" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P182" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R182" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S182" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T182" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U182" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V182" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W182" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X182" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA182" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB182" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC182" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD182" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE182" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF182" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG182" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH182" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI182" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ182" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK182" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL182" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM182" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN182" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO182" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP182" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ182" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR182" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS182" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT182" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU182" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV182" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW182" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX182" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY182" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ182" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA182" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB182" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC182" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD182" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE182" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF182" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG182" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH182" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI182" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ182" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK182" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL182" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM182" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN182" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO182" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP182" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ182" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR182" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="183">
@@ -39616,211 +39616,211 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C183" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K183" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L183" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M183" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N183" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O183" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P183" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q183" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R183" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S183" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T183" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U183" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V183" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W183" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X183" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA183" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB183" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC183" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD183" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE183" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF183" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG183" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH183" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI183" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ183" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK183" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL183" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM183" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN183" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO183" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP183" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ183" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR183" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS183" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT183" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU183" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV183" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW183" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX183" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY183" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ183" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA183" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB183" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC183" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD183" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE183" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF183" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG183" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH183" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI183" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ183" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK183" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL183" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM183" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN183" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO183" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP183" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ183" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR183" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="184">
@@ -39830,211 +39830,211 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>2.597</v>
+        <v>2.502</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>2.411</v>
+        <v>2.3435</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.919</v>
+        <v>2.729</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>2.389</v>
+        <v>2.305</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>2.6585</v>
+        <v>2.5635</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>2.1855</v>
+        <v>2.15</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="J184" s="3" t="n">
-        <v>2.371</v>
+        <v>2.2865</v>
       </c>
       <c r="K184" s="3" t="n">
-        <v>1.466</v>
+        <v>1.423</v>
       </c>
       <c r="L184" s="3" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>2.3045</v>
+        <v>2.247</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>2.3395</v>
+        <v>2.28</v>
       </c>
       <c r="O184" s="3" t="n">
-        <v>3.758</v>
+        <v>3.638</v>
       </c>
       <c r="P184" s="3" t="n">
-        <v>2.119</v>
+        <v>2.0145</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>2.769</v>
+        <v>2.675</v>
       </c>
       <c r="R184" s="3" t="n">
-        <v>2.6785</v>
+        <v>2.4885</v>
       </c>
       <c r="S184" s="3" t="n">
-        <v>2.9145</v>
+        <v>2.7245</v>
       </c>
       <c r="T184" s="3" t="n">
-        <v>2.2785</v>
+        <v>2.1915</v>
       </c>
       <c r="U184" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="V184" s="3" t="n">
-        <v>2.269</v>
+        <v>2.17</v>
       </c>
       <c r="W184" s="3" t="n">
-        <v>1.7885</v>
+        <v>1.7265</v>
       </c>
       <c r="X184" s="3" t="n">
-        <v>2.2675</v>
+        <v>2.2065</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.114</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>2.276</v>
+        <v>2.21</v>
       </c>
       <c r="AA184" s="3" t="n">
-        <v>2.38</v>
+        <v>2.315</v>
       </c>
       <c r="AB184" s="3" t="n">
-        <v>2.367</v>
+        <v>2.315</v>
       </c>
       <c r="AC184" s="3" t="n">
-        <v>2.5045</v>
+        <v>2.4185</v>
       </c>
       <c r="AD184" s="3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE184" s="3" t="n">
-        <v>2.149</v>
+        <v>2.1515</v>
       </c>
       <c r="AF184" s="3" t="n">
-        <v>3.535</v>
+        <v>3.4695</v>
       </c>
       <c r="AG184" s="3" t="n">
-        <v>2.616</v>
+        <v>2.515</v>
       </c>
       <c r="AH184" s="3" t="n">
-        <v>2.163</v>
+        <v>2.0975</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="AJ184" s="3" t="n">
-        <v>2.669</v>
+        <v>2.574</v>
       </c>
       <c r="AK184" s="3" t="n">
-        <v>2.3115</v>
+        <v>2.25</v>
       </c>
       <c r="AL184" s="3" t="n">
-        <v>1.972</v>
+        <v>1.8945</v>
       </c>
       <c r="AM184" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.6485</v>
       </c>
       <c r="AN184" s="3" t="n">
-        <v>3.627</v>
+        <v>3.513</v>
       </c>
       <c r="AO184" s="3" t="n">
-        <v>3.4325</v>
+        <v>3.375</v>
       </c>
       <c r="AP184" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2155</v>
       </c>
       <c r="AQ184" s="3" t="n">
-        <v>1.787</v>
+        <v>1.725</v>
       </c>
       <c r="AR184" s="3" t="n">
-        <v>2.5195</v>
+        <v>2.4295</v>
       </c>
       <c r="AS184" s="3" t="n">
-        <v>1.6695</v>
+        <v>1.595</v>
       </c>
       <c r="AT184" s="3" t="n">
-        <v>1.827</v>
+        <v>1.737</v>
       </c>
       <c r="AU184" s="3" t="n">
-        <v>2.209</v>
+        <v>2.1165</v>
       </c>
       <c r="AV184" s="3" t="n">
-        <v>2.562</v>
+        <v>2.467</v>
       </c>
       <c r="AW184" s="3" t="n">
-        <v>3.5155</v>
+        <v>3.413</v>
       </c>
       <c r="AX184" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4625</v>
       </c>
       <c r="AY184" s="3" t="n">
-        <v>2.1065</v>
+        <v>1.9895</v>
       </c>
       <c r="AZ184" s="3" t="n">
-        <v>2.459</v>
+        <v>2.3715</v>
       </c>
       <c r="BA184" s="3" t="n">
-        <v>1.8975</v>
+        <v>1.8125</v>
       </c>
       <c r="BB184" s="3" t="n">
-        <v>1.696</v>
+        <v>1.634</v>
       </c>
       <c r="BC184" s="3" t="n">
-        <v>3.121</v>
+        <v>2.931</v>
       </c>
       <c r="BD184" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.6935</v>
       </c>
       <c r="BE184" s="3" t="n">
-        <v>2.432</v>
+        <v>2.342</v>
       </c>
       <c r="BF184" s="3" t="n">
-        <v>2.0115</v>
+        <v>1.9175</v>
       </c>
       <c r="BG184" s="3" t="n">
-        <v>2.236</v>
+        <v>2.1485</v>
       </c>
       <c r="BH184" s="3" t="n">
-        <v>2.6745</v>
+        <v>2.5805</v>
       </c>
       <c r="BI184" s="3" t="n">
         <v>3.387</v>
       </c>
       <c r="BJ184" s="3" t="n">
-        <v>3.387</v>
+        <v>3.255</v>
       </c>
       <c r="BK184" s="3" t="n">
-        <v>1.697</v>
+        <v>1.6095</v>
       </c>
       <c r="BL184" s="3" t="n">
-        <v>3.0385</v>
+        <v>2.9485</v>
       </c>
       <c r="BM184" s="3" t="n">
-        <v>2.9335</v>
+        <v>2.8745</v>
       </c>
       <c r="BN184" s="3" t="n">
-        <v>3.564</v>
+        <v>3.505</v>
       </c>
       <c r="BO184" s="3" t="n">
-        <v>1.822</v>
+        <v>1.732</v>
       </c>
       <c r="BP184" s="3" t="n">
-        <v>1.9495</v>
+        <v>1.8595</v>
       </c>
       <c r="BQ184" s="3" t="n">
-        <v>2.405</v>
+        <v>2.3175</v>
       </c>
       <c r="BR184" s="3" t="n">
-        <v>1.5575</v>
+        <v>1.5145</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -33196,211 +33196,211 @@
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>2.5129</v>
+        <v>2.515</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>2.2411</v>
+        <v>2.24</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2.3218</v>
+        <v>2.32</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2.4706</v>
+        <v>2.47</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2.2164</v>
+        <v>2.215</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>2.2179</v>
+        <v>2.22</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>2.3431</v>
+        <v>2.345</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>2.3066</v>
+        <v>2.305</v>
       </c>
       <c r="K153" s="3" t="n">
-        <v>1.3453</v>
+        <v>1.34</v>
       </c>
       <c r="L153" s="3" t="n">
-        <v>1.2365</v>
+        <v>1.235</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>2.2632</v>
+        <v>2.28</v>
       </c>
       <c r="N153" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q153" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="S153" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="T153" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U153" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="V153" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="W153" s="3" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="X153" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="Y153" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z153" s="3" t="n">
         <v>2.325</v>
       </c>
-      <c r="O153" s="3" t="n">
-        <v>3.3634</v>
-      </c>
-      <c r="P153" s="3" t="n">
-        <v>2.0119</v>
-      </c>
-      <c r="Q153" s="3" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="R153" s="3" t="n">
-        <v>2.2573</v>
-      </c>
-      <c r="S153" s="3" t="n">
-        <v>2.3143</v>
-      </c>
-      <c r="T153" s="3" t="n">
-        <v>2.0671</v>
-      </c>
-      <c r="U153" s="3" t="n">
+      <c r="AA153" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB153" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AC153" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V153" s="3" t="n">
-        <v>2.3305</v>
-      </c>
-      <c r="W153" s="3" t="n">
-        <v>1.3227</v>
-      </c>
-      <c r="X153" s="3" t="n">
-        <v>2.3053</v>
-      </c>
-      <c r="Y153" s="3" t="n">
-        <v>2.0113</v>
-      </c>
-      <c r="Z153" s="3" t="n">
-        <v>2.3254</v>
-      </c>
-      <c r="AA153" s="3" t="n">
-        <v>2.298</v>
-      </c>
-      <c r="AB153" s="3" t="n">
-        <v>2.2965</v>
-      </c>
-      <c r="AC153" s="3" t="n">
-        <v>2.2153</v>
-      </c>
       <c r="AD153" s="3" t="n">
-        <v>2.45</v>
+        <v>2.735</v>
       </c>
       <c r="AE153" s="3" t="n">
-        <v>2.2356</v>
+        <v>2.235</v>
       </c>
       <c r="AF153" s="3" t="n">
-        <v>3.6106</v>
+        <v>3.61</v>
       </c>
       <c r="AG153" s="3" t="n">
-        <v>2.6998</v>
+        <v>2.7</v>
       </c>
       <c r="AH153" s="3" t="n">
-        <v>2.1737</v>
+        <v>2.175</v>
       </c>
       <c r="AI153" s="3" t="n">
-        <v>1.3354</v>
+        <v>1.35</v>
       </c>
       <c r="AJ153" s="3" t="n">
-        <v>2.4964</v>
+        <v>2.5</v>
       </c>
       <c r="AK153" s="3" t="n">
-        <v>2.26</v>
+        <v>2.295</v>
       </c>
       <c r="AL153" s="3" t="n">
-        <v>1.9808</v>
+        <v>1.98</v>
       </c>
       <c r="AM153" s="3" t="n">
-        <v>2.6219</v>
+        <v>2.63</v>
       </c>
       <c r="AN153" s="3" t="n">
-        <v>3.6325</v>
+        <v>3.635</v>
       </c>
       <c r="AO153" s="3" t="n">
-        <v>3.388</v>
+        <v>3.38</v>
       </c>
       <c r="AP153" s="3" t="n">
         <v>2.25</v>
       </c>
       <c r="AQ153" s="3" t="n">
-        <v>1.2537</v>
+        <v>1.255</v>
       </c>
       <c r="AR153" s="3" t="n">
-        <v>2.3024</v>
+        <v>2.3</v>
       </c>
       <c r="AS153" s="3" t="n">
-        <v>1.2027</v>
+        <v>1.205</v>
       </c>
       <c r="AT153" s="3" t="n">
-        <v>1.3344</v>
+        <v>1.335</v>
       </c>
       <c r="AU153" s="3" t="n">
-        <v>2.041</v>
+        <v>2.045</v>
       </c>
       <c r="AV153" s="3" t="n">
-        <v>2.4382</v>
+        <v>2.44</v>
       </c>
       <c r="AW153" s="3" t="n">
-        <v>3.5022</v>
+        <v>3.5</v>
       </c>
       <c r="AX153" s="3" t="n">
-        <v>2.4308</v>
+        <v>2.43</v>
       </c>
       <c r="AY153" s="3" t="n">
-        <v>2.013</v>
+        <v>2.015</v>
       </c>
       <c r="AZ153" s="3" t="n">
-        <v>1.9834</v>
+        <v>2.085</v>
       </c>
       <c r="BA153" s="3" t="n">
-        <v>1.4894</v>
+        <v>1.495</v>
       </c>
       <c r="BB153" s="3" t="n">
-        <v>1.2904</v>
+        <v>1.29</v>
       </c>
       <c r="BC153" s="3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD153" s="3" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BE153" s="3" t="n">
-        <v>2.3216</v>
+        <v>2.32</v>
       </c>
       <c r="BF153" s="3" t="n">
-        <v>1.3344</v>
+        <v>1.34</v>
       </c>
       <c r="BG153" s="3" t="n">
-        <v>2.0059</v>
+        <v>2.005</v>
       </c>
       <c r="BH153" s="3" t="n">
-        <v>2.3617</v>
+        <v>2.36</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>3.2284</v>
+        <v>3.225</v>
       </c>
       <c r="BJ153" s="3" t="n">
-        <v>3.2134</v>
+        <v>3.215</v>
       </c>
       <c r="BK153" s="3" t="n">
-        <v>1.3002</v>
+        <v>1.3</v>
       </c>
       <c r="BL153" s="3" t="n">
-        <v>3.2134</v>
+        <v>2.94</v>
       </c>
       <c r="BM153" s="3" t="n">
-        <v>3.1938</v>
+        <v>2.4</v>
       </c>
       <c r="BN153" s="3" t="n">
-        <v>3.1938</v>
+        <v>3.19</v>
       </c>
       <c r="BO153" s="3" t="n">
-        <v>1.2844</v>
+        <v>1.32</v>
       </c>
       <c r="BP153" s="3" t="n">
-        <v>1.4214</v>
+        <v>1.43</v>
       </c>
       <c r="BQ153" s="3" t="n">
-        <v>2.2889</v>
+        <v>2.29</v>
       </c>
       <c r="BR153" s="3" t="n">
-        <v>1.2477</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="154">
@@ -33410,211 +33410,211 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>2.5129</v>
+        <v>2.515</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2.2411</v>
+        <v>2.24</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2.3218</v>
+        <v>2.32</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2.4706</v>
+        <v>2.47</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2.2164</v>
+        <v>2.215</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>2.2179</v>
+        <v>2.22</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>2.3431</v>
+        <v>2.345</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>2.3066</v>
+        <v>2.305</v>
       </c>
       <c r="K154" s="3" t="n">
-        <v>1.3453</v>
+        <v>1.34</v>
       </c>
       <c r="L154" s="3" t="n">
-        <v>1.2365</v>
+        <v>1.235</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>2.2632</v>
+        <v>2.28</v>
       </c>
       <c r="N154" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O154" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P154" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q154" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R154" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="S154" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="T154" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U154" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="V154" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="W154" s="3" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="X154" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="Y154" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z154" s="3" t="n">
         <v>2.325</v>
       </c>
-      <c r="O154" s="3" t="n">
-        <v>3.3634</v>
-      </c>
-      <c r="P154" s="3" t="n">
-        <v>2.0119</v>
-      </c>
-      <c r="Q154" s="3" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="R154" s="3" t="n">
-        <v>2.2573</v>
-      </c>
-      <c r="S154" s="3" t="n">
-        <v>2.3143</v>
-      </c>
-      <c r="T154" s="3" t="n">
-        <v>2.0671</v>
-      </c>
-      <c r="U154" s="3" t="n">
+      <c r="AA154" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB154" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AC154" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V154" s="3" t="n">
-        <v>2.3305</v>
-      </c>
-      <c r="W154" s="3" t="n">
-        <v>1.3227</v>
-      </c>
-      <c r="X154" s="3" t="n">
-        <v>2.3053</v>
-      </c>
-      <c r="Y154" s="3" t="n">
-        <v>2.0113</v>
-      </c>
-      <c r="Z154" s="3" t="n">
-        <v>2.3254</v>
-      </c>
-      <c r="AA154" s="3" t="n">
-        <v>2.298</v>
-      </c>
-      <c r="AB154" s="3" t="n">
-        <v>2.2965</v>
-      </c>
-      <c r="AC154" s="3" t="n">
-        <v>2.2153</v>
-      </c>
       <c r="AD154" s="3" t="n">
-        <v>2.45</v>
+        <v>2.735</v>
       </c>
       <c r="AE154" s="3" t="n">
-        <v>2.2356</v>
+        <v>2.235</v>
       </c>
       <c r="AF154" s="3" t="n">
-        <v>3.6106</v>
+        <v>3.61</v>
       </c>
       <c r="AG154" s="3" t="n">
-        <v>2.6998</v>
+        <v>2.7</v>
       </c>
       <c r="AH154" s="3" t="n">
-        <v>2.1737</v>
+        <v>2.175</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>1.3354</v>
+        <v>1.35</v>
       </c>
       <c r="AJ154" s="3" t="n">
-        <v>2.4964</v>
+        <v>2.5</v>
       </c>
       <c r="AK154" s="3" t="n">
-        <v>2.26</v>
+        <v>2.295</v>
       </c>
       <c r="AL154" s="3" t="n">
-        <v>1.9808</v>
+        <v>1.98</v>
       </c>
       <c r="AM154" s="3" t="n">
-        <v>2.6219</v>
+        <v>2.63</v>
       </c>
       <c r="AN154" s="3" t="n">
-        <v>3.6325</v>
+        <v>3.635</v>
       </c>
       <c r="AO154" s="3" t="n">
-        <v>3.388</v>
+        <v>3.38</v>
       </c>
       <c r="AP154" s="3" t="n">
         <v>2.25</v>
       </c>
       <c r="AQ154" s="3" t="n">
-        <v>1.2537</v>
+        <v>1.255</v>
       </c>
       <c r="AR154" s="3" t="n">
-        <v>2.3024</v>
+        <v>2.3</v>
       </c>
       <c r="AS154" s="3" t="n">
-        <v>1.2027</v>
+        <v>1.205</v>
       </c>
       <c r="AT154" s="3" t="n">
-        <v>1.3344</v>
+        <v>1.335</v>
       </c>
       <c r="AU154" s="3" t="n">
-        <v>2.041</v>
+        <v>2.045</v>
       </c>
       <c r="AV154" s="3" t="n">
-        <v>2.4382</v>
+        <v>2.44</v>
       </c>
       <c r="AW154" s="3" t="n">
-        <v>3.5022</v>
+        <v>3.5</v>
       </c>
       <c r="AX154" s="3" t="n">
-        <v>2.4308</v>
+        <v>2.43</v>
       </c>
       <c r="AY154" s="3" t="n">
-        <v>2.013</v>
+        <v>2.015</v>
       </c>
       <c r="AZ154" s="3" t="n">
-        <v>1.9834</v>
+        <v>2.085</v>
       </c>
       <c r="BA154" s="3" t="n">
-        <v>1.4894</v>
+        <v>1.495</v>
       </c>
       <c r="BB154" s="3" t="n">
-        <v>1.2904</v>
+        <v>1.29</v>
       </c>
       <c r="BC154" s="3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD154" s="3" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BE154" s="3" t="n">
-        <v>2.3216</v>
+        <v>2.32</v>
       </c>
       <c r="BF154" s="3" t="n">
-        <v>1.3344</v>
+        <v>1.34</v>
       </c>
       <c r="BG154" s="3" t="n">
-        <v>2.0059</v>
+        <v>2.005</v>
       </c>
       <c r="BH154" s="3" t="n">
-        <v>2.3617</v>
+        <v>2.36</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>3.2284</v>
+        <v>3.225</v>
       </c>
       <c r="BJ154" s="3" t="n">
-        <v>3.2134</v>
+        <v>3.215</v>
       </c>
       <c r="BK154" s="3" t="n">
-        <v>1.3002</v>
+        <v>1.3</v>
       </c>
       <c r="BL154" s="3" t="n">
-        <v>3.2134</v>
+        <v>2.94</v>
       </c>
       <c r="BM154" s="3" t="n">
-        <v>3.1938</v>
+        <v>2.4</v>
       </c>
       <c r="BN154" s="3" t="n">
-        <v>3.1938</v>
+        <v>3.19</v>
       </c>
       <c r="BO154" s="3" t="n">
-        <v>1.2844</v>
+        <v>1.32</v>
       </c>
       <c r="BP154" s="3" t="n">
-        <v>1.4214</v>
+        <v>1.43</v>
       </c>
       <c r="BQ154" s="3" t="n">
-        <v>2.2889</v>
+        <v>2.29</v>
       </c>
       <c r="BR154" s="3" t="n">
-        <v>1.2477</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="155">
@@ -33624,211 +33624,211 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>2.502</v>
+        <v>2.3199</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>2.3435</v>
+        <v>1.8696</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>2.729</v>
+        <v>1.3025</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>2.305</v>
+        <v>1.8668</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.055</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2.14</v>
+        <v>1.8209</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>2.15</v>
+        <v>1.8688</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>2.2865</v>
+        <v>2.041</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>2.2865</v>
+        <v>1.9548</v>
       </c>
       <c r="K155" s="3" t="n">
-        <v>1.423</v>
+        <v>1.4833</v>
       </c>
       <c r="L155" s="3" t="n">
-        <v>1.6</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>2.247</v>
+        <v>1.7927</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>3.638</v>
+        <v>3.6035</v>
       </c>
       <c r="P155" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.7402</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>2.675</v>
+        <v>2.3977</v>
       </c>
       <c r="R155" s="3" t="n">
-        <v>2.4885</v>
+        <v>1.8034</v>
       </c>
       <c r="S155" s="3" t="n">
-        <v>2.7245</v>
+        <v>1.9442</v>
       </c>
       <c r="T155" s="3" t="n">
-        <v>2.1915</v>
+        <v>1.7188</v>
       </c>
       <c r="U155" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.4076</v>
       </c>
       <c r="V155" s="3" t="n">
-        <v>2.17</v>
+        <v>1.9556</v>
       </c>
       <c r="W155" s="3" t="n">
-        <v>1.7265</v>
+        <v>0.9443</v>
       </c>
       <c r="X155" s="3" t="n">
-        <v>2.2065</v>
+        <v>1.8438</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>2.114</v>
+        <v>1.5255</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>2.21</v>
+        <v>1.8589</v>
       </c>
       <c r="AA155" s="3" t="n">
-        <v>2.315</v>
+        <v>2.0097</v>
       </c>
       <c r="AB155" s="3" t="n">
-        <v>2.315</v>
+        <v>2.0002</v>
       </c>
       <c r="AC155" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.4</v>
       </c>
       <c r="AD155" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE155" s="3" t="n">
-        <v>2.1515</v>
+        <v>1.5542</v>
       </c>
       <c r="AF155" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.4178</v>
       </c>
       <c r="AG155" s="3" t="n">
-        <v>2.515</v>
+        <v>2.4729</v>
       </c>
       <c r="AH155" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.5885</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>1.491</v>
+        <v>1.4387</v>
       </c>
       <c r="AJ155" s="3" t="n">
-        <v>2.574</v>
+        <v>2.3183</v>
       </c>
       <c r="AK155" s="3" t="n">
-        <v>2.25</v>
+        <v>1.8933</v>
       </c>
       <c r="AL155" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.457</v>
       </c>
       <c r="AM155" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.5744</v>
       </c>
       <c r="AN155" s="3" t="n">
-        <v>3.513</v>
+        <v>3.4551</v>
       </c>
       <c r="AO155" s="3" t="n">
-        <v>3.375</v>
+        <v>3.4706</v>
       </c>
       <c r="AP155" s="3" t="n">
-        <v>2.2155</v>
+        <v>1.7363</v>
       </c>
       <c r="AQ155" s="3" t="n">
-        <v>1.725</v>
+        <v>0.9848</v>
       </c>
       <c r="AR155" s="3" t="n">
-        <v>2.4295</v>
+        <v>2</v>
       </c>
       <c r="AS155" s="3" t="n">
-        <v>1.595</v>
+        <v>1.0142</v>
       </c>
       <c r="AT155" s="3" t="n">
-        <v>1.737</v>
+        <v>1.1183</v>
       </c>
       <c r="AU155" s="3" t="n">
-        <v>2.1165</v>
+        <v>1.6704</v>
       </c>
       <c r="AV155" s="3" t="n">
-        <v>2.467</v>
+        <v>2.2961</v>
       </c>
       <c r="AW155" s="3" t="n">
-        <v>3.413</v>
+        <v>3.4043</v>
       </c>
       <c r="AX155" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.1984</v>
       </c>
       <c r="AY155" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.6052</v>
       </c>
       <c r="AZ155" s="3" t="n">
-        <v>2.3715</v>
+        <v>1.5813</v>
       </c>
       <c r="BA155" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.1893</v>
       </c>
       <c r="BB155" s="3" t="n">
-        <v>1.634</v>
+        <v>0.7859</v>
       </c>
       <c r="BC155" s="3" t="n">
-        <v>2.931</v>
+        <v>1.5025</v>
       </c>
       <c r="BD155" s="3" t="n">
-        <v>2.6935</v>
+        <v>1.3025</v>
       </c>
       <c r="BE155" s="3" t="n">
-        <v>2.342</v>
+        <v>1.848</v>
       </c>
       <c r="BF155" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.1183</v>
       </c>
       <c r="BG155" s="3" t="n">
-        <v>2.1485</v>
+        <v>1.7186</v>
       </c>
       <c r="BH155" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.3168</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>3.387</v>
+        <v>3.4155</v>
       </c>
       <c r="BJ155" s="3" t="n">
-        <v>3.255</v>
+        <v>3.4535</v>
       </c>
       <c r="BK155" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.0046</v>
       </c>
       <c r="BL155" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.4535</v>
       </c>
       <c r="BM155" s="3" t="n">
-        <v>2.8745</v>
+        <v>3.4982</v>
       </c>
       <c r="BN155" s="3" t="n">
-        <v>3.505</v>
+        <v>3.4982</v>
       </c>
       <c r="BO155" s="3" t="n">
-        <v>1.732</v>
+        <v>1.0683</v>
       </c>
       <c r="BP155" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.0028</v>
       </c>
       <c r="BQ155" s="3" t="n">
-        <v>2.3175</v>
+        <v>1.7907</v>
       </c>
       <c r="BR155" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.4588</v>
       </c>
     </row>
     <row r="156">
@@ -33838,211 +33838,211 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>2.502</v>
+        <v>2.3199</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2.3435</v>
+        <v>1.8696</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>2.729</v>
+        <v>1.3025</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2.305</v>
+        <v>1.8668</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.055</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2.14</v>
+        <v>1.8209</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>2.15</v>
+        <v>1.8688</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>2.2865</v>
+        <v>2.041</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>2.2865</v>
+        <v>1.9548</v>
       </c>
       <c r="K156" s="3" t="n">
-        <v>1.423</v>
+        <v>1.4833</v>
       </c>
       <c r="L156" s="3" t="n">
-        <v>1.6</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>2.247</v>
+        <v>1.7927</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>3.638</v>
+        <v>3.6035</v>
       </c>
       <c r="P156" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.7402</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>2.675</v>
+        <v>2.3977</v>
       </c>
       <c r="R156" s="3" t="n">
-        <v>2.4885</v>
+        <v>1.8034</v>
       </c>
       <c r="S156" s="3" t="n">
-        <v>2.7245</v>
+        <v>1.9442</v>
       </c>
       <c r="T156" s="3" t="n">
-        <v>2.1915</v>
+        <v>1.7188</v>
       </c>
       <c r="U156" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.4076</v>
       </c>
       <c r="V156" s="3" t="n">
-        <v>2.17</v>
+        <v>1.9556</v>
       </c>
       <c r="W156" s="3" t="n">
-        <v>1.7265</v>
+        <v>0.9443</v>
       </c>
       <c r="X156" s="3" t="n">
-        <v>2.2065</v>
+        <v>1.8438</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>2.114</v>
+        <v>1.5255</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>2.21</v>
+        <v>1.8589</v>
       </c>
       <c r="AA156" s="3" t="n">
-        <v>2.315</v>
+        <v>2.0097</v>
       </c>
       <c r="AB156" s="3" t="n">
-        <v>2.315</v>
+        <v>2.0002</v>
       </c>
       <c r="AC156" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.4</v>
       </c>
       <c r="AD156" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE156" s="3" t="n">
-        <v>2.1515</v>
+        <v>1.5542</v>
       </c>
       <c r="AF156" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.4178</v>
       </c>
       <c r="AG156" s="3" t="n">
-        <v>2.515</v>
+        <v>2.4729</v>
       </c>
       <c r="AH156" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.5885</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>1.491</v>
+        <v>1.4387</v>
       </c>
       <c r="AJ156" s="3" t="n">
-        <v>2.574</v>
+        <v>2.3183</v>
       </c>
       <c r="AK156" s="3" t="n">
-        <v>2.25</v>
+        <v>1.8933</v>
       </c>
       <c r="AL156" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.457</v>
       </c>
       <c r="AM156" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.5744</v>
       </c>
       <c r="AN156" s="3" t="n">
-        <v>3.513</v>
+        <v>3.4551</v>
       </c>
       <c r="AO156" s="3" t="n">
-        <v>3.375</v>
+        <v>3.4706</v>
       </c>
       <c r="AP156" s="3" t="n">
-        <v>2.2155</v>
+        <v>1.7363</v>
       </c>
       <c r="AQ156" s="3" t="n">
-        <v>1.725</v>
+        <v>0.9848</v>
       </c>
       <c r="AR156" s="3" t="n">
-        <v>2.4295</v>
+        <v>2</v>
       </c>
       <c r="AS156" s="3" t="n">
-        <v>1.595</v>
+        <v>1.0142</v>
       </c>
       <c r="AT156" s="3" t="n">
-        <v>1.737</v>
+        <v>1.1183</v>
       </c>
       <c r="AU156" s="3" t="n">
-        <v>2.1165</v>
+        <v>1.6704</v>
       </c>
       <c r="AV156" s="3" t="n">
-        <v>2.467</v>
+        <v>2.2961</v>
       </c>
       <c r="AW156" s="3" t="n">
-        <v>3.413</v>
+        <v>3.4043</v>
       </c>
       <c r="AX156" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.1984</v>
       </c>
       <c r="AY156" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.6052</v>
       </c>
       <c r="AZ156" s="3" t="n">
-        <v>2.3715</v>
+        <v>1.5813</v>
       </c>
       <c r="BA156" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.1893</v>
       </c>
       <c r="BB156" s="3" t="n">
-        <v>1.634</v>
+        <v>0.7859</v>
       </c>
       <c r="BC156" s="3" t="n">
-        <v>2.931</v>
+        <v>1.5025</v>
       </c>
       <c r="BD156" s="3" t="n">
-        <v>2.6935</v>
+        <v>1.3025</v>
       </c>
       <c r="BE156" s="3" t="n">
-        <v>2.342</v>
+        <v>1.848</v>
       </c>
       <c r="BF156" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.1183</v>
       </c>
       <c r="BG156" s="3" t="n">
-        <v>2.1485</v>
+        <v>1.7186</v>
       </c>
       <c r="BH156" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.3168</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>3.387</v>
+        <v>3.4155</v>
       </c>
       <c r="BJ156" s="3" t="n">
-        <v>3.255</v>
+        <v>3.4535</v>
       </c>
       <c r="BK156" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.0046</v>
       </c>
       <c r="BL156" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.4535</v>
       </c>
       <c r="BM156" s="3" t="n">
-        <v>2.8745</v>
+        <v>3.4982</v>
       </c>
       <c r="BN156" s="3" t="n">
-        <v>3.505</v>
+        <v>3.4982</v>
       </c>
       <c r="BO156" s="3" t="n">
-        <v>1.732</v>
+        <v>1.0683</v>
       </c>
       <c r="BP156" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.0028</v>
       </c>
       <c r="BQ156" s="3" t="n">
-        <v>2.3175</v>
+        <v>1.7907</v>
       </c>
       <c r="BR156" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.4588</v>
       </c>
     </row>
     <row r="157">
@@ -34052,211 +34052,211 @@
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G157" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M157" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N157" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H157" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I157" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J157" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K157" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L157" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M157" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N157" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O157" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P157" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R157" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S157" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T157" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U157" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V157" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W157" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X157" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA157" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB157" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC157" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD157" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE157" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF157" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG157" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH157" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ157" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK157" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL157" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM157" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN157" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO157" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP157" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ157" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR157" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS157" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT157" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU157" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV157" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW157" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX157" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY157" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ157" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA157" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB157" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC157" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD157" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE157" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF157" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG157" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH157" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ157" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK157" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL157" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM157" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN157" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO157" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP157" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ157" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR157" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="158">
@@ -34266,211 +34266,211 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G158" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K158" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N158" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H158" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I158" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J158" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K158" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L158" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M158" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N158" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O158" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P158" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R158" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S158" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T158" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U158" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V158" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W158" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X158" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA158" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB158" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC158" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD158" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE158" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF158" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG158" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH158" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ158" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK158" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL158" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM158" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN158" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO158" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP158" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ158" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR158" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS158" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT158" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU158" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV158" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW158" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX158" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY158" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ158" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA158" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB158" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC158" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD158" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE158" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF158" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG158" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH158" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ158" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK158" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL158" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM158" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN158" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO158" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP158" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ158" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR158" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="159">
@@ -34480,211 +34480,211 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C159" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G159" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L159" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N159" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H159" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I159" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J159" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K159" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L159" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M159" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N159" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O159" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P159" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R159" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S159" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T159" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U159" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V159" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W159" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X159" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA159" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB159" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC159" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD159" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE159" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF159" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG159" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH159" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI159" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ159" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK159" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL159" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM159" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN159" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO159" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP159" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ159" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR159" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS159" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT159" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU159" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV159" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW159" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX159" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY159" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ159" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA159" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB159" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC159" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD159" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE159" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF159" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG159" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH159" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ159" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK159" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL159" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM159" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN159" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO159" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP159" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ159" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR159" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="160">
@@ -34694,211 +34694,211 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G160" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K160" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L160" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N160" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H160" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I160" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J160" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K160" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L160" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M160" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N160" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O160" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P160" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R160" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S160" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T160" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U160" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V160" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W160" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X160" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA160" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB160" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC160" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD160" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE160" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF160" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG160" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH160" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ160" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK160" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL160" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM160" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN160" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO160" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP160" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ160" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR160" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS160" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT160" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU160" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV160" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW160" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX160" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY160" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ160" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA160" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB160" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC160" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD160" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE160" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF160" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG160" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH160" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ160" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK160" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL160" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM160" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN160" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO160" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP160" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ160" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR160" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="161">
@@ -34908,211 +34908,211 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C161" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G161" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N161" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H161" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I161" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J161" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K161" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L161" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M161" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N161" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O161" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P161" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q161" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R161" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S161" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T161" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U161" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V161" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W161" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X161" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA161" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB161" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC161" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD161" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE161" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF161" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG161" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH161" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ161" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK161" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL161" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM161" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN161" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO161" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP161" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ161" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR161" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS161" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT161" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU161" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV161" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW161" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX161" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY161" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ161" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA161" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB161" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC161" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD161" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE161" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF161" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG161" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH161" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ161" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK161" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL161" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM161" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN161" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO161" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP161" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ161" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR161" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="162">
@@ -35122,211 +35122,211 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G162" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K162" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N162" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H162" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I162" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J162" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K162" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L162" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M162" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N162" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O162" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P162" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R162" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S162" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T162" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U162" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V162" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W162" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X162" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA162" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB162" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC162" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD162" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE162" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF162" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG162" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH162" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ162" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK162" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL162" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM162" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN162" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO162" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP162" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ162" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR162" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS162" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT162" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU162" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV162" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW162" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX162" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY162" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ162" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA162" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB162" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC162" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD162" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE162" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF162" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG162" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH162" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ162" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK162" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL162" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM162" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN162" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO162" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP162" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ162" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR162" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="163">
@@ -35336,211 +35336,211 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G163" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M163" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N163" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H163" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I163" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J163" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K163" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L163" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M163" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N163" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O163" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P163" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R163" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S163" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T163" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U163" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V163" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W163" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X163" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA163" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB163" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC163" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD163" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE163" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF163" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG163" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH163" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ163" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK163" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL163" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM163" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN163" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO163" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP163" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ163" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR163" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS163" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT163" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU163" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV163" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW163" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX163" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY163" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ163" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA163" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB163" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC163" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD163" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE163" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF163" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG163" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH163" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ163" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK163" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL163" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM163" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN163" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO163" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP163" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ163" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR163" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="164">
@@ -35550,211 +35550,211 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G164" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M164" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N164" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H164" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I164" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J164" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K164" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L164" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M164" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N164" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O164" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P164" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R164" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S164" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T164" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U164" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V164" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W164" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X164" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y164" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA164" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB164" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC164" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD164" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE164" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF164" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG164" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH164" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI164" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ164" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM164" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN164" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO164" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP164" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ164" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR164" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS164" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT164" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU164" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV164" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW164" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX164" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY164" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ164" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA164" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB164" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC164" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD164" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE164" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF164" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG164" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH164" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ164" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK164" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL164" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM164" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN164" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO164" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP164" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ164" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR164" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="165">
@@ -35764,211 +35764,211 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G165" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K165" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M165" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N165" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H165" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I165" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J165" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K165" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L165" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M165" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N165" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O165" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P165" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R165" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S165" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T165" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U165" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V165" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W165" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X165" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA165" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB165" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC165" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD165" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE165" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF165" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG165" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH165" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI165" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ165" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK165" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL165" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM165" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN165" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO165" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP165" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ165" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR165" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS165" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT165" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU165" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV165" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW165" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX165" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY165" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ165" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA165" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB165" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC165" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD165" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE165" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF165" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG165" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH165" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ165" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK165" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL165" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM165" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN165" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO165" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP165" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ165" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR165" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="166">
@@ -35978,211 +35978,211 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G166" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K166" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M166" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N166" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H166" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I166" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J166" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K166" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L166" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M166" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N166" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O166" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P166" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R166" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S166" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T166" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U166" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V166" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W166" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X166" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA166" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB166" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC166" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD166" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE166" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF166" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG166" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH166" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI166" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ166" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK166" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL166" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM166" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN166" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO166" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP166" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ166" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR166" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS166" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT166" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU166" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV166" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW166" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX166" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY166" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ166" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA166" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB166" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC166" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD166" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE166" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF166" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG166" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH166" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI166" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ166" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK166" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL166" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM166" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN166" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO166" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP166" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ166" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR166" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="167">
@@ -36192,211 +36192,211 @@
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C167" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G167" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M167" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N167" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H167" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I167" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J167" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K167" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L167" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M167" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N167" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O167" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P167" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R167" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S167" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T167" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U167" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V167" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W167" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X167" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA167" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC167" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD167" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE167" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF167" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG167" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH167" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ167" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM167" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN167" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO167" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP167" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ167" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR167" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS167" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT167" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU167" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV167" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW167" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX167" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY167" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ167" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA167" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB167" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC167" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD167" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE167" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF167" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG167" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH167" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI167" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ167" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK167" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL167" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM167" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN167" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO167" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP167" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ167" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR167" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="168">
@@ -36406,211 +36406,211 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G168" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K168" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M168" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N168" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H168" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I168" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J168" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K168" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L168" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M168" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N168" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O168" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P168" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R168" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S168" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T168" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U168" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V168" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W168" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X168" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA168" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC168" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD168" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE168" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF168" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG168" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH168" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ168" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM168" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN168" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO168" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP168" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ168" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR168" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS168" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT168" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU168" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV168" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW168" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX168" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY168" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ168" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA168" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB168" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC168" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD168" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE168" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF168" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG168" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH168" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI168" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ168" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK168" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL168" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM168" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN168" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO168" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP168" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ168" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR168" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="169">
@@ -36620,211 +36620,211 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G169" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K169" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M169" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N169" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H169" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I169" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J169" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K169" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L169" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M169" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N169" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O169" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P169" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R169" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S169" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T169" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U169" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V169" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W169" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X169" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA169" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB169" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC169" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD169" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE169" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF169" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG169" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH169" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ169" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK169" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM169" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN169" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO169" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP169" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ169" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR169" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS169" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT169" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU169" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV169" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW169" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX169" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY169" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ169" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA169" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB169" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC169" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD169" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE169" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF169" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG169" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH169" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI169" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ169" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK169" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL169" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM169" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN169" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO169" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP169" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ169" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR169" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="170">
@@ -36834,211 +36834,211 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G170" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K170" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L170" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M170" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N170" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H170" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I170" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J170" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K170" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L170" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M170" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N170" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O170" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P170" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R170" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S170" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T170" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U170" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V170" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W170" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X170" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA170" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB170" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC170" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD170" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE170" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF170" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG170" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH170" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI170" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ170" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK170" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL170" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM170" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN170" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO170" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP170" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ170" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR170" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS170" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT170" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU170" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV170" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW170" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX170" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY170" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ170" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA170" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB170" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC170" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD170" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE170" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF170" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG170" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH170" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI170" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ170" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK170" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL170" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM170" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN170" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO170" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP170" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ170" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR170" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="171">
@@ -37048,211 +37048,211 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C171" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G171" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J171" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K171" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L171" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M171" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N171" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H171" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I171" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J171" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K171" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L171" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M171" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N171" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O171" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P171" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R171" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S171" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T171" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U171" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V171" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W171" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X171" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA171" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB171" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC171" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD171" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE171" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF171" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG171" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH171" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI171" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ171" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK171" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL171" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM171" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN171" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO171" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP171" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ171" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR171" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS171" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT171" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU171" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV171" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW171" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX171" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY171" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ171" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA171" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB171" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC171" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD171" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE171" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF171" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG171" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH171" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI171" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ171" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK171" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL171" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM171" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN171" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO171" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP171" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ171" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR171" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="172">
@@ -37262,211 +37262,211 @@
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G172" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K172" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L172" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M172" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N172" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H172" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I172" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J172" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K172" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L172" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M172" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N172" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O172" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P172" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R172" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S172" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T172" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U172" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V172" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W172" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X172" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA172" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB172" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC172" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD172" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE172" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF172" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG172" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH172" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI172" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ172" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK172" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL172" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM172" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN172" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO172" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP172" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ172" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR172" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS172" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT172" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU172" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV172" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW172" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX172" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY172" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ172" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA172" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB172" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC172" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD172" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE172" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF172" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG172" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH172" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI172" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ172" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK172" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL172" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM172" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN172" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO172" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP172" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ172" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR172" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="173">
@@ -37476,211 +37476,211 @@
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G173" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M173" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N173" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H173" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I173" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J173" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K173" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L173" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M173" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N173" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O173" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P173" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R173" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S173" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T173" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U173" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V173" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W173" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X173" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA173" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB173" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC173" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD173" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE173" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF173" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG173" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH173" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI173" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ173" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK173" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM173" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN173" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO173" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP173" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ173" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR173" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS173" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT173" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU173" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV173" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW173" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX173" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY173" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ173" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA173" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB173" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC173" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD173" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE173" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF173" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG173" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH173" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI173" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ173" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK173" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL173" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM173" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN173" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO173" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP173" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ173" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR173" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="174">
@@ -37690,211 +37690,211 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G174" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K174" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L174" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M174" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N174" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H174" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I174" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J174" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K174" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L174" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M174" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N174" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O174" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P174" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R174" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S174" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T174" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U174" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V174" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W174" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X174" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA174" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB174" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC174" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD174" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE174" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF174" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG174" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH174" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI174" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ174" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK174" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM174" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN174" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO174" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP174" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ174" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR174" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS174" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT174" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU174" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV174" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW174" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX174" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY174" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ174" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA174" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB174" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC174" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD174" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE174" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF174" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG174" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH174" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI174" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ174" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK174" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL174" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM174" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN174" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO174" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP174" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ174" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR174" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="175">
@@ -37904,211 +37904,211 @@
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C175" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G175" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H175" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K175" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M175" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N175" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H175" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I175" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J175" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K175" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L175" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M175" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N175" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O175" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P175" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R175" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S175" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T175" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U175" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V175" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W175" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X175" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA175" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB175" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC175" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD175" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE175" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF175" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG175" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH175" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ175" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK175" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM175" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN175" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO175" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP175" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ175" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR175" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS175" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT175" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU175" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV175" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW175" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX175" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY175" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ175" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA175" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB175" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC175" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD175" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE175" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF175" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG175" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH175" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI175" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ175" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK175" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL175" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM175" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN175" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO175" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP175" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ175" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR175" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="176">
@@ -38118,211 +38118,211 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G176" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K176" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L176" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M176" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N176" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H176" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I176" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J176" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K176" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L176" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M176" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N176" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O176" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P176" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R176" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S176" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T176" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U176" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V176" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W176" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X176" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA176" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB176" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC176" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD176" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE176" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF176" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG176" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH176" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ176" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK176" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL176" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM176" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN176" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO176" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP176" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ176" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR176" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS176" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT176" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU176" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV176" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW176" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX176" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY176" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ176" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA176" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB176" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC176" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD176" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE176" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF176" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG176" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH176" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI176" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ176" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK176" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL176" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM176" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN176" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO176" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP176" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ176" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR176" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="177">
@@ -38332,211 +38332,211 @@
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G177" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H177" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K177" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L177" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M177" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N177" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H177" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I177" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J177" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K177" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L177" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M177" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N177" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O177" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P177" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R177" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S177" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T177" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U177" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V177" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W177" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X177" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA177" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB177" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC177" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD177" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE177" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF177" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG177" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH177" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ177" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL177" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM177" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN177" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO177" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP177" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ177" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR177" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS177" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT177" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU177" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV177" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW177" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX177" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY177" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ177" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA177" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB177" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC177" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD177" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE177" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF177" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG177" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH177" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI177" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ177" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK177" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL177" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM177" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN177" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO177" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP177" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ177" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR177" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="178">
@@ -38546,211 +38546,211 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G178" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J178" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K178" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L178" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M178" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N178" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H178" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I178" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J178" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K178" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L178" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M178" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N178" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O178" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P178" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R178" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S178" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T178" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U178" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V178" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W178" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X178" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA178" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB178" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC178" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD178" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE178" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF178" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG178" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH178" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ178" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK178" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL178" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM178" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN178" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO178" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP178" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ178" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR178" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS178" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT178" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU178" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV178" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW178" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX178" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY178" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ178" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA178" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB178" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC178" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD178" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE178" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF178" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG178" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH178" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI178" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ178" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK178" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL178" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM178" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN178" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO178" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP178" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ178" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR178" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="179">
@@ -38760,211 +38760,211 @@
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C179" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G179" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K179" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M179" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N179" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H179" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I179" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J179" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K179" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L179" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M179" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N179" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O179" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P179" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q179" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R179" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S179" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T179" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U179" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V179" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W179" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X179" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y179" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z179" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA179" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB179" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC179" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD179" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE179" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF179" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG179" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH179" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ179" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK179" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM179" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN179" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO179" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP179" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ179" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR179" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS179" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT179" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU179" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV179" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW179" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX179" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY179" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ179" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA179" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB179" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC179" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD179" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE179" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF179" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG179" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH179" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI179" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ179" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK179" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL179" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM179" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN179" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO179" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP179" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ179" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR179" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="180">
@@ -38974,211 +38974,211 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G180" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J180" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K180" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L180" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M180" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N180" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H180" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I180" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J180" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K180" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L180" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M180" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N180" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O180" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P180" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R180" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S180" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T180" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U180" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V180" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W180" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X180" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA180" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB180" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC180" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD180" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE180" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF180" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG180" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH180" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ180" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK180" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL180" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM180" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN180" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO180" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP180" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ180" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR180" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS180" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT180" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU180" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV180" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW180" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX180" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY180" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ180" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA180" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB180" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC180" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD180" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE180" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF180" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG180" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH180" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI180" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ180" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK180" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL180" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM180" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN180" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO180" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP180" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ180" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR180" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="181">
@@ -39188,211 +39188,211 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C181" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G181" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K181" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L181" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M181" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N181" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H181" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I181" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J181" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K181" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L181" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M181" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N181" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O181" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P181" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R181" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S181" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T181" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U181" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V181" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W181" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X181" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA181" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB181" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC181" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD181" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE181" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF181" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG181" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH181" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI181" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ181" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK181" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL181" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM181" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN181" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO181" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP181" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ181" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR181" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS181" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT181" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU181" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV181" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW181" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX181" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY181" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ181" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA181" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB181" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC181" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD181" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE181" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF181" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG181" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH181" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI181" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ181" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK181" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL181" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM181" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN181" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO181" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP181" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ181" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR181" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="182">
@@ -39402,211 +39402,211 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G182" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K182" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L182" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M182" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N182" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H182" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I182" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J182" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K182" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L182" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M182" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N182" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O182" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P182" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R182" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S182" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T182" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U182" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V182" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W182" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X182" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA182" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB182" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC182" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD182" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE182" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF182" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG182" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH182" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI182" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ182" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK182" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL182" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM182" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN182" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO182" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP182" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ182" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR182" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS182" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT182" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU182" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV182" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW182" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX182" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY182" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ182" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA182" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB182" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC182" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD182" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE182" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF182" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG182" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH182" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI182" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ182" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK182" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL182" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM182" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN182" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO182" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP182" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ182" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR182" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="183">
@@ -39616,211 +39616,211 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C183" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G183" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K183" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L183" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M183" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N183" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H183" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I183" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J183" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K183" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L183" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M183" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N183" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O183" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P183" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q183" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R183" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S183" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T183" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U183" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V183" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W183" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X183" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA183" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB183" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC183" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD183" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE183" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF183" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG183" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH183" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI183" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ183" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK183" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL183" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM183" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN183" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO183" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP183" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ183" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR183" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS183" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT183" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU183" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV183" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW183" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX183" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY183" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ183" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA183" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB183" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC183" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD183" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE183" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF183" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG183" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH183" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI183" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ183" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK183" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL183" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM183" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN183" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO183" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP183" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ183" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR183" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="184">
@@ -39830,211 +39830,211 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>2.502</v>
+        <v>2.424</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>2.3435</v>
+        <v>2.173</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.729</v>
+        <v>2.57</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>2.305</v>
+        <v>2.227</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.4855</v>
       </c>
       <c r="G184" s="3" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>2.1735</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="K184" s="3" t="n">
+        <v>1.3285</v>
+      </c>
+      <c r="L184" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M184" s="3" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="N184" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="H184" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I184" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="J184" s="3" t="n">
-        <v>2.2865</v>
-      </c>
-      <c r="K184" s="3" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="L184" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M184" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="N184" s="3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O184" s="3" t="n">
-        <v>3.638</v>
+        <v>3.59</v>
       </c>
       <c r="P184" s="3" t="n">
-        <v>2.0145</v>
+        <v>1.908</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>2.675</v>
+        <v>2.597</v>
       </c>
       <c r="R184" s="3" t="n">
-        <v>2.4885</v>
+        <v>2.3295</v>
       </c>
       <c r="S184" s="3" t="n">
-        <v>2.7245</v>
+        <v>2.5655</v>
       </c>
       <c r="T184" s="3" t="n">
-        <v>2.1915</v>
+        <v>2.085</v>
       </c>
       <c r="U184" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="V184" s="3" t="n">
-        <v>2.17</v>
+        <v>2.1345</v>
       </c>
       <c r="W184" s="3" t="n">
-        <v>1.7265</v>
+        <v>1.6465</v>
       </c>
       <c r="X184" s="3" t="n">
-        <v>2.2065</v>
+        <v>2.1285</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>2.114</v>
+        <v>2.036</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>2.21</v>
+        <v>2.117</v>
       </c>
       <c r="AA184" s="3" t="n">
-        <v>2.315</v>
+        <v>2.145</v>
       </c>
       <c r="AB184" s="3" t="n">
-        <v>2.315</v>
+        <v>2.1345</v>
       </c>
       <c r="AC184" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.389</v>
       </c>
       <c r="AD184" s="3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AE184" s="3" t="n">
-        <v>2.1515</v>
+        <v>2.0735</v>
       </c>
       <c r="AF184" s="3" t="n">
-        <v>3.4695</v>
+        <v>3.45</v>
       </c>
       <c r="AG184" s="3" t="n">
-        <v>2.515</v>
+        <v>2.5</v>
       </c>
       <c r="AH184" s="3" t="n">
-        <v>2.0975</v>
+        <v>1.927</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>1.491</v>
+        <v>1.3965</v>
       </c>
       <c r="AJ184" s="3" t="n">
-        <v>2.574</v>
+        <v>2.496</v>
       </c>
       <c r="AK184" s="3" t="n">
-        <v>2.25</v>
+        <v>2.135</v>
       </c>
       <c r="AL184" s="3" t="n">
-        <v>1.8945</v>
+        <v>1.8165</v>
       </c>
       <c r="AM184" s="3" t="n">
-        <v>2.6485</v>
+        <v>2.7045</v>
       </c>
       <c r="AN184" s="3" t="n">
-        <v>3.513</v>
+        <v>3.5995</v>
       </c>
       <c r="AO184" s="3" t="n">
-        <v>3.375</v>
+        <v>3.297</v>
       </c>
       <c r="AP184" s="3" t="n">
-        <v>2.2155</v>
+        <v>2.1375</v>
       </c>
       <c r="AQ184" s="3" t="n">
-        <v>1.725</v>
+        <v>1.645</v>
       </c>
       <c r="AR184" s="3" t="n">
-        <v>2.4295</v>
+        <v>2.3515</v>
       </c>
       <c r="AS184" s="3" t="n">
-        <v>1.595</v>
+        <v>1.517</v>
       </c>
       <c r="AT184" s="3" t="n">
-        <v>1.737</v>
+        <v>1.659</v>
       </c>
       <c r="AU184" s="3" t="n">
-        <v>2.1165</v>
+        <v>2.0385</v>
       </c>
       <c r="AV184" s="3" t="n">
-        <v>2.467</v>
+        <v>2.424</v>
       </c>
       <c r="AW184" s="3" t="n">
-        <v>3.413</v>
+        <v>3.335</v>
       </c>
       <c r="AX184" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3845</v>
       </c>
       <c r="AY184" s="3" t="n">
-        <v>1.9895</v>
+        <v>1.9115</v>
       </c>
       <c r="AZ184" s="3" t="n">
-        <v>2.3715</v>
+        <v>2.2935</v>
       </c>
       <c r="BA184" s="3" t="n">
-        <v>1.8125</v>
+        <v>1.7345</v>
       </c>
       <c r="BB184" s="3" t="n">
-        <v>1.634</v>
+        <v>1.554</v>
       </c>
       <c r="BC184" s="3" t="n">
-        <v>2.931</v>
+        <v>2.772</v>
       </c>
       <c r="BD184" s="3" t="n">
-        <v>2.6935</v>
+        <v>2.5345</v>
       </c>
       <c r="BE184" s="3" t="n">
-        <v>2.342</v>
+        <v>2.264</v>
       </c>
       <c r="BF184" s="3" t="n">
-        <v>1.9175</v>
+        <v>1.8395</v>
       </c>
       <c r="BG184" s="3" t="n">
-        <v>2.1485</v>
+        <v>2.0705</v>
       </c>
       <c r="BH184" s="3" t="n">
-        <v>2.5805</v>
+        <v>2.5025</v>
       </c>
       <c r="BI184" s="3" t="n">
-        <v>3.387</v>
+        <v>3.222</v>
       </c>
       <c r="BJ184" s="3" t="n">
-        <v>3.255</v>
+        <v>3.247</v>
       </c>
       <c r="BK184" s="3" t="n">
-        <v>1.6095</v>
+        <v>1.5315</v>
       </c>
       <c r="BL184" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.034</v>
       </c>
       <c r="BM184" s="3" t="n">
-        <v>2.8745</v>
+        <v>2.7965</v>
       </c>
       <c r="BN184" s="3" t="n">
-        <v>3.505</v>
+        <v>3.427</v>
       </c>
       <c r="BO184" s="3" t="n">
-        <v>1.732</v>
+        <v>1.654</v>
       </c>
       <c r="BP184" s="3" t="n">
-        <v>1.8595</v>
+        <v>1.7815</v>
       </c>
       <c r="BQ184" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.2395</v>
       </c>
       <c r="BR184" s="3" t="n">
-        <v>1.5145</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
